--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\Design-Space-Explorer\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99DCBBB-9DCD-4BDD-9692-A2BB1D8AF8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D87267D-7651-48DB-929A-CC62EBF2202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="420">
   <si>
     <t>dimension_id</t>
   </si>
@@ -116,21 +116,9 @@
     <t>metaphorical-proximity-to-data</t>
   </si>
   <si>
-    <t>metaphorical-proximity-to-reality</t>
-  </si>
-  <si>
     <t>Metaphorical Proximity to Data</t>
   </si>
   <si>
-    <t>Metaphorical Proximity to Reality</t>
-  </si>
-  <si>
-    <t>#f06952</t>
-  </si>
-  <si>
-    <t>#f06953</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/icons/data.png"</t>
   </si>
   <si>
@@ -200,9 +188,6 @@
     <t>Physical Mechanisms</t>
   </si>
   <si>
-    <t>#d494ff</t>
-  </si>
-  <si>
     <t>#436d41</t>
   </si>
   <si>
@@ -266,9 +251,6 @@
     <t>Scene</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/arrangement.png"</t>
-  </si>
-  <si>
     <t>level-1</t>
   </si>
   <si>
@@ -434,9 +416,6 @@
     <t>density</t>
   </si>
   <si>
-    <t>spatial-arrangement</t>
-  </si>
-  <si>
     <t>lighting</t>
   </si>
   <si>
@@ -515,9 +494,6 @@
     <t>Lighting</t>
   </si>
   <si>
-    <t>Spatial Arrangement</t>
-  </si>
-  <si>
     <t>Density</t>
   </si>
   <si>
@@ -995,9 +971,6 @@
     <t>Cinematic, compositional and presentation elements.</t>
   </si>
   <si>
-    <t>ex-024</t>
-  </si>
-  <si>
     <t>ex-030</t>
   </si>
   <si>
@@ -1119,6 +1092,198 @@
   </si>
   <si>
     <t>"/Design-Space-Explorer/design_space_static/scene.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/cut.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/count.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/speed.png"</t>
+  </si>
+  <si>
+    <t>This dimension focuses on photorealism in digital media: material appearance, lighting and shading, texture detail, shadows, and depth cues (e.g., perspective). It evaluates how “photo-like” the element looks, independent of what it represents or how abstract this representation may be. We also don’t evaluate how well its motion matches what it represents (captured in real-world representation).</t>
+  </si>
+  <si>
+    <t>Visual Realism</t>
+  </si>
+  <si>
+    <t>Real-World Familiarity</t>
+  </si>
+  <si>
+    <t>real-world-familiarity</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/icons/realism.png"</t>
+  </si>
+  <si>
+    <t>visual-realism</t>
+  </si>
+  <si>
+    <t>low-realism</t>
+  </si>
+  <si>
+    <t>intermediate-realism</t>
+  </si>
+  <si>
+    <t>high-realism</t>
+  </si>
+  <si>
+    <t>The element is highly stylized, with minimal or no attempt to imitate a photorealistic appearance.</t>
+  </si>
+  <si>
+    <t>The element includes some realistic aspects, such as depth, lighting, or texture, but these are mixed with stylized aspects.</t>
+  </si>
+  <si>
+    <t>Strong resemblance to physical reality through detailed materials, lighting, shadows, and depth cues. Photographs of physical artefacts also belong to this category.</t>
+  </si>
+  <si>
+    <t>High (Visually Realistic)</t>
+  </si>
+  <si>
+    <t>Intermediate (Mixed Realism)</t>
+  </si>
+  <si>
+    <t>Low (Stylized)</t>
+  </si>
+  <si>
+    <t>ex-014</t>
+  </si>
+  <si>
+    <t>ex-025</t>
+  </si>
+  <si>
+    <t>#6D451A</t>
+  </si>
+  <si>
+    <t>alignment</t>
+  </si>
+  <si>
+    <t>Alignment</t>
+  </si>
+  <si>
+    <t>adjacent_placement</t>
+  </si>
+  <si>
+    <t>Adjacent Placement</t>
+  </si>
+  <si>
+    <t>bonding</t>
+  </si>
+  <si>
+    <t>Bonding</t>
+  </si>
+  <si>
+    <t>branching</t>
+  </si>
+  <si>
+    <t>clustering</t>
+  </si>
+  <si>
+    <t>geographical_placement</t>
+  </si>
+  <si>
+    <t>packing</t>
+  </si>
+  <si>
+    <t>piling</t>
+  </si>
+  <si>
+    <t>scattering</t>
+  </si>
+  <si>
+    <t>stacking</t>
+  </si>
+  <si>
+    <t>topological_placement</t>
+  </si>
+  <si>
+    <t>trajectory</t>
+  </si>
+  <si>
+    <t>Branching</t>
+  </si>
+  <si>
+    <t>Clustering</t>
+  </si>
+  <si>
+    <t>Packing</t>
+  </si>
+  <si>
+    <t>Piling</t>
+  </si>
+  <si>
+    <t>Scattering</t>
+  </si>
+  <si>
+    <t>Stacking</t>
+  </si>
+  <si>
+    <t>Trajectory</t>
+  </si>
+  <si>
+    <t>Geographical Placement</t>
+  </si>
+  <si>
+    <t>Topological Placement</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/adjacent_placement.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/bonding.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/alignment.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/branching.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/clustering.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/geographical_placement.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/packing.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/piling.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/scattering.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/stacking.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/topological_placement.png"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/trajectory.png"</t>
+  </si>
+  <si>
+    <t>ex-064</t>
+  </si>
+  <si>
+    <t>ex-049</t>
+  </si>
+  <si>
+    <t>ex-020</t>
+  </si>
+  <si>
+    <t>ex-052</t>
+  </si>
+  <si>
+    <t>ex-027</t>
+  </si>
+  <si>
+    <t>ex-080</t>
+  </si>
+  <si>
+    <t>ex-058</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="31.21875" customWidth="1"/>
@@ -1547,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1576,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1588,7 +1753,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1602,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>28</v>
@@ -1614,7 +1779,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1622,25 +1787,25 @@
     </row>
     <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1648,25 +1813,25 @@
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>361</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -1674,321 +1839,348 @@
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>329</v>
+        <v>30</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7" s="5">
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
+        <v>301</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>320</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>66</v>
+        <v>319</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5">
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5">
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B11" s="5">
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5">
         <v>2</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>314</v>
+      </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5">
-        <v>4</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>314</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C13" s="5"/>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="H13">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5">
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>46</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>239</v>
+        <v>53</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>248</v>
+        <v>55</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>316</v>
-      </c>
+      <c r="C17" s="5"/>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="5">
+        <v>3</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H18">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.77734375" customWidth="1"/>
@@ -2030,10 +2222,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>26</v>
@@ -2047,24 +2239,24 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
@@ -2075,24 +2267,24 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2103,13 +2295,13 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2118,7 +2310,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
       <c r="K4" s="8" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2129,24 +2321,24 @@
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
       <c r="K5" s="8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="L5" s="5">
         <v>4</v>
@@ -2157,13 +2349,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2172,7 +2364,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="6"/>
       <c r="K6" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L6" s="5">
         <v>5</v>
@@ -2183,24 +2375,24 @@
         <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
       <c r="K7" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="L7" s="5">
         <v>6</v>
@@ -2211,16 +2403,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -2237,16 +2429,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -2263,16 +2455,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2289,16 +2481,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2310,571 +2502,597 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>98</v>
+        <v>373</v>
       </c>
       <c r="D12" t="s">
-        <v>321</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>374</v>
+      </c>
       <c r="L12" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>100</v>
+        <v>366</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="8"/>
+      <c r="K13" s="8" t="s">
+        <v>210</v>
+      </c>
       <c r="L13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="5" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>104</v>
+        <v>367</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>105</v>
+        <v>371</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>107</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="8"/>
+      <c r="K14" s="8" t="s">
+        <v>220</v>
+      </c>
       <c r="L14" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="8"/>
+      <c r="K15" s="8" t="s">
+        <v>286</v>
+      </c>
       <c r="L15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="8"/>
+      <c r="K16" s="8" t="s">
+        <v>374</v>
+      </c>
       <c r="L16" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="K17" s="8" t="s">
+        <v>220</v>
+      </c>
       <c r="L17" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18"/>
+        <v>313</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="K18" s="9" t="s">
-        <v>326</v>
+        <v>31</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="8" t="s">
+        <v>375</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19"/>
+        <v>96</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="F19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="K19" s="9" t="s">
-        <v>221</v>
+        <v>31</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="8" t="s">
+        <v>374</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" s="5" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20"/>
+        <v>100</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="F20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I20" s="9"/>
+        <v>31</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="8" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L20" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="E21"/>
       <c r="F21" s="6" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>208</v>
+        <v>188</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="K21" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>171</v>
+        <v>115</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="E22"/>
       <c r="F22" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>222</v>
+        <v>189</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="K22" s="9" t="s">
+        <v>213</v>
       </c>
       <c r="L22" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" t="s">
-        <v>170</v>
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E23"/>
       <c r="F23" s="6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="I23" s="9"/>
       <c r="K23" s="8" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="L23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>66</v>
+        <v>319</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="L24" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D25" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>211</v>
+        <v>192</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="L25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" t="s">
         <v>167</v>
       </c>
-      <c r="D26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="L26" s="5">
+      <c r="F27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L27" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>300</v>
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" t="s">
+        <v>168</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="K28" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="L28" s="5"/>
+        <v>203</v>
+      </c>
+      <c r="L28" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>302</v>
+        <v>126</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>169</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="L29" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" t="s">
-        <v>178</v>
+        <v>290</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
       <c r="K30" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="L30" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" t="s">
-        <v>179</v>
+        <v>291</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="L31" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" t="s">
-        <v>180</v>
+        <v>293</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="L32" s="5">
-        <v>2</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="K32" s="8"/>
+      <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="I33" s="8"/>
+      <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -2882,51 +3100,48 @@
     </row>
     <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>210</v>
+        <v>357</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="L34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>290</v>
+        <v>59</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="L35" s="5">
         <v>2</v>
@@ -2934,634 +3149,977 @@
     </row>
     <row r="36" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="C36" t="s">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="L36" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>140</v>
+        <v>381</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>382</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="L37" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>141</v>
+        <v>377</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="L38" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>142</v>
+        <v>383</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>392</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="L39" s="5">
-        <v>3</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>143</v>
+        <v>384</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>393</v>
       </c>
       <c r="D40" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="J40" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L40" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="C41" t="s">
-        <v>155</v>
+        <v>399</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>406</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="L41" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>254</v>
+        <v>386</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="D42" t="s">
-        <v>264</v>
-      </c>
-      <c r="F42" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="K42" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="L42" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>263</v>
+        <v>387</v>
       </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>395</v>
       </c>
       <c r="D43" t="s">
-        <v>265</v>
-      </c>
-      <c r="F43" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>408</v>
+      </c>
       <c r="K43" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="L43" s="5">
-        <v>4</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>262</v>
+        <v>388</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>396</v>
       </c>
       <c r="D44" t="s">
-        <v>266</v>
-      </c>
-      <c r="F44" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="G44" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="J44" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="L44" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>261</v>
+        <v>389</v>
       </c>
       <c r="C45" t="s">
-        <v>258</v>
+        <v>397</v>
       </c>
       <c r="D45" t="s">
-        <v>267</v>
-      </c>
-      <c r="F45" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>410</v>
+      </c>
       <c r="K45" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="L45" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>400</v>
       </c>
       <c r="D46" t="s">
-        <v>268</v>
-      </c>
-      <c r="F46" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>411</v>
+      </c>
       <c r="K46" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="L46" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>145</v>
+        <v>391</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>398</v>
       </c>
       <c r="D47" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="J47" t="s">
-        <v>347</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="L47" s="5">
-        <v>1</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="J48" t="s">
-        <v>343</v>
+        <v>194</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="L48" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>289</v>
+        <v>131</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>154</v>
       </c>
       <c r="D49" t="s">
-        <v>270</v>
-      </c>
-      <c r="F49" s="6"/>
+        <v>175</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="G49" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>336</v>
+        <v>199</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="L49" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" t="s">
+        <v>176</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="L50" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C50" t="s">
-        <v>271</v>
-      </c>
-      <c r="D50" t="s">
-        <v>272</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="L50" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>152</v>
       </c>
       <c r="D51" t="s">
-        <v>274</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="J51" t="s">
-        <v>349</v>
+        <v>177</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>291</v>
+        <v>221</v>
       </c>
       <c r="L51" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>286</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="D52" t="s">
-        <v>282</v>
-      </c>
-      <c r="F52" s="6"/>
+        <v>178</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>358</v>
+      </c>
       <c r="K52" s="10" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="L52" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>285</v>
+        <v>135</v>
       </c>
       <c r="C53" t="s">
-        <v>276</v>
+        <v>150</v>
       </c>
       <c r="D53" t="s">
-        <v>281</v>
-      </c>
-      <c r="F53" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="K53" s="10" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="L53" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="C54" t="s">
-        <v>277</v>
+        <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="6"/>
-      <c r="K54" s="10" t="s">
-        <v>213</v>
+        <v>180</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="J54" t="s">
+        <v>332</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="L54" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
-        <v>278</v>
+        <v>148</v>
       </c>
       <c r="D55" t="s">
-        <v>279</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="K55" s="10" t="s">
-        <v>294</v>
+        <v>181</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="L55" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>147</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
-        <v>192</v>
+        <v>256</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="K56" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="L56" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="D57" t="s">
-        <v>193</v>
+        <v>257</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="K57" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="L57" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="D58" t="s">
-        <v>194</v>
+        <v>258</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="J58" t="s">
+        <v>343</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="L58" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>241</v>
+        <v>253</v>
+      </c>
+      <c r="C59" t="s">
+        <v>250</v>
       </c>
       <c r="D59" t="s">
-        <v>252</v>
+        <v>259</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="K59" s="8" t="s">
+        <v>318</v>
       </c>
       <c r="L59" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>240</v>
+        <v>252</v>
+      </c>
+      <c r="C60" t="s">
+        <v>251</v>
       </c>
       <c r="D60" t="s">
-        <v>253</v>
+        <v>260</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="K60" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="L60" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>250</v>
+        <v>138</v>
+      </c>
+      <c r="C61" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" t="s">
+        <v>182</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="J61" t="s">
+        <v>338</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="L61" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>251</v>
+        <v>139</v>
+      </c>
+      <c r="C62" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="J62" t="s">
+        <v>334</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>219</v>
       </c>
       <c r="L62" s="5">
         <v>2</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" t="s">
+        <v>261</v>
+      </c>
+      <c r="D63" t="s">
+        <v>262</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="L63" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C64" t="s">
+        <v>263</v>
+      </c>
+      <c r="D64" t="s">
+        <v>264</v>
+      </c>
+      <c r="F64" s="6"/>
+      <c r="L64" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C65" t="s">
+        <v>265</v>
+      </c>
+      <c r="D65" t="s">
+        <v>266</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="J65" t="s">
+        <v>340</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="L65" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C66" t="s">
+        <v>267</v>
+      </c>
+      <c r="D66" t="s">
+        <v>274</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="K66" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="L66" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C67" t="s">
+        <v>268</v>
+      </c>
+      <c r="D67" t="s">
+        <v>273</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="K67" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="L67" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C68" t="s">
+        <v>269</v>
+      </c>
+      <c r="D68" t="s">
+        <v>272</v>
+      </c>
+      <c r="F68" s="6"/>
+      <c r="K68" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="L68" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69" t="s">
+        <v>270</v>
+      </c>
+      <c r="D69" t="s">
+        <v>271</v>
+      </c>
+      <c r="F69" s="6"/>
+      <c r="K69" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="L69" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="L70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" t="s">
+        <v>185</v>
+      </c>
+      <c r="L71" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" t="s">
+        <v>186</v>
+      </c>
+      <c r="L72" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73" t="s">
+        <v>244</v>
+      </c>
+      <c r="L73" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D74" t="s">
+        <v>245</v>
+      </c>
+      <c r="L74" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L75" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="L76" s="5">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J49" r:id="rId1" xr:uid="{F4001A4E-147C-4DA1-B793-B80C3CDB6A5D}"/>
+    <hyperlink ref="J63" r:id="rId1" xr:uid="{F4001A4E-147C-4DA1-B793-B80C3CDB6A5D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D87267D-7651-48DB-929A-CC62EBF2202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12B7F36-292D-43C1-98A1-FE0B2D80214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="447">
   <si>
     <t>dimension_id</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Low Proximity (Symbolic)</t>
   </si>
   <si>
-    <t>["No resemblance to data", "Requires learned conventions", "Abstract relationship"]</t>
-  </si>
-  <si>
     <t>intermediate-proximity-iconic</t>
   </si>
   <si>
@@ -317,9 +314,6 @@
     <t>The visual element shares some similar qualities or resembles in an intuitive way the associated data/theme.</t>
   </si>
   <si>
-    <t>["Shares similar qualities", "Intuitive resemblance", "Some visual connection"]</t>
-  </si>
-  <si>
     <t>high-proximity-literal</t>
   </si>
   <si>
@@ -329,45 +323,24 @@
     <t>The visual element is closely (physically/causally) connected to the data/theme.</t>
   </si>
   <si>
-    <t>["Close physical connection", "Causal relationship", "Direct representation"]</t>
-  </si>
-  <si>
     <t>low-proximity-slightly-familiar</t>
   </si>
   <si>
-    <t>Low Proximity (Slightly Familiar)</t>
-  </si>
-  <si>
     <t>The visual element is only slightly familiar / feels more abstract or unfamiliar.</t>
   </si>
   <si>
-    <t>["Abstract feeling", "Unfamiliar to most", "Limited real-world connection"]</t>
-  </si>
-  <si>
     <t>intermediate-proximity-moderately-familiar</t>
   </si>
   <si>
-    <t>Intermediate Proximity (Moderately Familiar)</t>
-  </si>
-  <si>
     <t>The visual element is moderately familiar.</t>
   </si>
   <si>
-    <t>["Some familiarity", "Known but not common", "Moderate recognition"]</t>
-  </si>
-  <si>
     <t>high-proximity-very-familiar</t>
   </si>
   <si>
-    <t>High Proximity (Very Familiar)</t>
-  </si>
-  <si>
     <t>The visual element is very familiar from everyday experience.</t>
   </si>
   <si>
-    <t>["Everyday experience", "Highly recognizable", "Strong real-world knowledge"]</t>
-  </si>
-  <si>
     <t>The object's location within the composition.</t>
   </si>
   <si>
@@ -617,9 +590,6 @@
     <t>"/Design-Space-Explorer/design_space_static/material.png"</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/transformations.png"</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/design_space_static/stretch.png"</t>
   </si>
   <si>
@@ -1052,15 +1022,6 @@
     <t>"/Design-Space-Explorer/videos/state_change.gif"</t>
   </si>
   <si>
-    <t>@marctudisco</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/marctudisco/</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/videos/infection.gif"</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/design_space_static/fluids.png"</t>
   </si>
   <si>
@@ -1284,6 +1245,126 @@
   </si>
   <si>
     <t>ex-058</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/material_transformation.png"</t>
+  </si>
+  <si>
+    <t>ex-009</t>
+  </si>
+  <si>
+    <t>Low (Unfamiliar)</t>
+  </si>
+  <si>
+    <t>Intermediate (Slightly Familiar)</t>
+  </si>
+  <si>
+    <t>High (Familiar)</t>
+  </si>
+  <si>
+    <t>ex-032</t>
+  </si>
+  <si>
+    <t>ex-039</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/waves.mp4"</t>
+  </si>
+  <si>
+    <t>@finnberenbroek</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/finnberenbroek/?g=5</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/vacades/?g=5</t>
+  </si>
+  <si>
+    <t>@vacades</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/fire.mp4"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/particles.mp4"</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/albacor_/</t>
+  </si>
+  <si>
+    <t>@albacor_</t>
+  </si>
+  <si>
+    <t>@kristoffermoth</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/weathering.mp4"</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kristoffermoth/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/emilsvfx/</t>
+  </si>
+  <si>
+    <t>@emilsvfx</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/optics.mp4"</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/split_vzn/</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/rhythms.mp4"</t>
+  </si>
+  <si>
+    <t>@split_vzn</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zachdarren/</t>
+  </si>
+  <si>
+    <t>@zachdarren</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/life_cycle.mp4"</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/vfx_media/</t>
+  </si>
+  <si>
+    <t>@vfx_media</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/decay.mp4"</t>
+  </si>
+  <si>
+    <t>@aiaskokkalis</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/movement.mp4"</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aiaskokkalis/</t>
+  </si>
+  <si>
+    <t>@lucasmagdaleni</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lucasmagdaleni/</t>
+  </si>
+  <si>
+    <t>@stephanhelbing</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/stephanhelbing/</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/infection.mp4"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/videos/patterns.mp4"</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1392,6 +1473,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1712,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1741,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1753,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1767,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>28</v>
@@ -1779,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1787,16 +1869,16 @@
     </row>
     <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -1805,7 +1887,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1813,16 +1895,16 @@
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>24</v>
@@ -1845,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
@@ -1871,10 +1953,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
@@ -1897,7 +1979,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -1909,7 +1991,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1923,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D9" t="s">
         <v>52</v>
@@ -1949,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -1969,13 +2051,13 @@
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B11" s="5">
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -2001,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2051,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -2077,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -2097,25 +2179,25 @@
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2123,23 +2205,23 @@
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2153,19 +2235,19 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -2222,10 +2304,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>26</v>
@@ -2245,18 +2327,18 @@
         <v>63</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="8" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
@@ -2278,13 +2360,13 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2301,7 +2383,7 @@
         <v>68</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2310,7 +2392,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
       <c r="K4" s="8" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2327,18 +2409,18 @@
         <v>70</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
       <c r="K5" s="8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L5" s="5">
         <v>4</v>
@@ -2355,7 +2437,7 @@
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2364,7 +2446,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="6"/>
       <c r="K6" s="8" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="L6" s="5">
         <v>5</v>
@@ -2381,18 +2463,18 @@
         <v>74</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
       <c r="K7" s="8" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="L7" s="5">
         <v>6</v>
@@ -2504,27 +2586,27 @@
     </row>
     <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -2532,27 +2614,27 @@
     </row>
     <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D13" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8" t="s">
-        <v>210</v>
+        <v>412</v>
       </c>
       <c r="L13" s="5">
         <v>2</v>
@@ -2560,48 +2642,46 @@
     </row>
     <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D14" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
       <c r="J14" s="6"/>
       <c r="K14" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L14" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>103</v>
+        <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>105</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
         <v>32</v>
       </c>
@@ -2610,28 +2690,26 @@
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
         <v>32</v>
       </c>
@@ -2640,41 +2718,39 @@
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>111</v>
+        <v>411</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>113</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>220</v>
+        <v>408</v>
       </c>
       <c r="L17" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>29</v>
       </c>
@@ -2685,11 +2761,9 @@
         <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>313</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>93</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
         <v>31</v>
       </c>
@@ -2698,28 +2772,26 @@
       <c r="I18" s="8"/>
       <c r="J18" s="6"/>
       <c r="K18" s="8" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" t="s">
         <v>95</v>
       </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>97</v>
-      </c>
+      <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
         <v>31</v>
       </c>
@@ -2728,7 +2800,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="6"/>
       <c r="K19" s="8" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
@@ -2739,17 +2811,15 @@
         <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>101</v>
-      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
         <v>31</v>
       </c>
@@ -2758,7 +2828,7 @@
       <c r="I20" s="8"/>
       <c r="J20" s="6"/>
       <c r="K20" s="8" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="L20" s="5">
         <v>3</v>
@@ -2775,18 +2845,18 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
@@ -2797,24 +2867,24 @@
         <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="L22" s="5">
         <v>2</v>
@@ -2825,24 +2895,24 @@
         <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I23" s="9"/>
       <c r="K23" s="8" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="L23" s="5">
         <v>3</v>
@@ -2859,16 +2929,16 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L24" s="5">
         <v>1</v>
@@ -2879,22 +2949,22 @@
         <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L25" s="5">
         <v>2</v>
@@ -2905,22 +2975,22 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L26" s="5">
         <v>1</v>
@@ -2931,22 +3001,22 @@
         <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -2957,22 +3027,22 @@
         <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="L28" s="5">
         <v>1</v>
@@ -2983,19 +3053,19 @@
         <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="L29" s="5">
         <v>2</v>
@@ -3006,24 +3076,24 @@
         <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
       <c r="K30" s="8" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L30" s="5"/>
     </row>
@@ -3032,19 +3102,19 @@
         <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="L31" s="5"/>
     </row>
@@ -3053,16 +3123,16 @@
         <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3072,27 +3142,27 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -3100,25 +3170,25 @@
     </row>
     <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="L34" s="5">
         <v>1</v>
@@ -3126,22 +3196,22 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="L35" s="5">
         <v>2</v>
@@ -3149,289 +3219,289 @@
     </row>
     <row r="36" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="C37" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C38" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D39" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C40" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="C41" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="D41" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G41" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="K41" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="C42" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="D42" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="C43" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="C44" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="C45" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="D45" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="D46" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="C47" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="D47" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="L47" s="5"/>
     </row>
@@ -3440,22 +3510,22 @@
         <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="L48" s="5">
         <v>1</v>
@@ -3466,22 +3536,22 @@
         <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="L49" s="5">
         <v>2</v>
@@ -3492,22 +3562,22 @@
         <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L50" s="5">
         <v>3</v>
@@ -3518,19 +3588,19 @@
         <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>57</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="L51" s="5">
         <v>1</v>
@@ -3541,22 +3611,22 @@
         <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D52" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="L52" s="5">
         <v>2</v>
@@ -3567,19 +3637,19 @@
         <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>57</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="L53" s="5">
         <v>3</v>
@@ -3590,96 +3660,123 @@
         <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J54" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="L54" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>56</v>
       </c>
+      <c r="H55" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>435</v>
+      </c>
       <c r="K55" s="8" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="L55" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C56" t="s">
+        <v>237</v>
+      </c>
+      <c r="D56" t="s">
         <v>246</v>
       </c>
-      <c r="C56" t="s">
-        <v>247</v>
-      </c>
-      <c r="D56" t="s">
-        <v>256</v>
-      </c>
       <c r="F56" s="6"/>
+      <c r="H56" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="J56" t="s">
+        <v>440</v>
+      </c>
       <c r="K56" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L56" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D57" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F57" s="6"/>
+      <c r="H57" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>429</v>
+      </c>
       <c r="K57" s="8" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="L57" s="5">
         <v>4</v>
@@ -3690,71 +3787,89 @@
         <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D58" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>344</v>
+        <v>445</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>342</v>
+        <v>441</v>
       </c>
       <c r="J58" t="s">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="L58" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C59" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D59" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F59" s="6"/>
+      <c r="H59" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="J59" t="s">
+        <v>444</v>
+      </c>
       <c r="K59" s="8" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L59" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D60" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F60" s="6"/>
+      <c r="H60" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>432</v>
+      </c>
       <c r="K60" s="8" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="L60" s="5">
         <v>7</v>
@@ -3765,31 +3880,31 @@
         <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" t="s">
         <v>138</v>
       </c>
-      <c r="C61" t="s">
-        <v>147</v>
-      </c>
       <c r="D61" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="J61" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L61" s="5">
         <v>1</v>
@@ -3800,31 +3915,31 @@
         <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="J62" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="L62" s="5">
         <v>2</v>
@@ -3835,48 +3950,57 @@
         <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D63" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="L63" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F64" s="6"/>
+      <c r="H64" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>417</v>
+      </c>
       <c r="L64" s="5">
         <v>4</v>
       </c>
@@ -3886,113 +4010,149 @@
         <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C65" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D65" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="J65" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="L65" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D66" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F66" s="6"/>
+      <c r="H66" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="J66" t="s">
+        <v>421</v>
+      </c>
       <c r="K66" s="10" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="L66" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C67" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D67" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F67" s="6"/>
+      <c r="H67" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="J67" t="s">
+        <v>416</v>
+      </c>
       <c r="K67" s="10" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="L67" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C68" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F68" s="6"/>
+      <c r="H68" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="J68" t="s">
+        <v>426</v>
+      </c>
       <c r="K68" s="10" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="L68" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C69" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D69" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F69" s="6"/>
+      <c r="H69" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="J69" t="s">
+        <v>425</v>
+      </c>
       <c r="K69" s="10" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="L69" s="5">
         <v>9</v>
@@ -4003,13 +4163,13 @@
         <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
@@ -4020,13 +4180,13 @@
         <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
@@ -4037,13 +4197,13 @@
         <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D72" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>
@@ -4051,16 +4211,16 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D73" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="L73" s="5">
         <v>1</v>
@@ -4068,16 +4228,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="L74" s="5">
         <v>2</v>
@@ -4085,16 +4245,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="L75" s="5">
         <v>1</v>
@@ -4102,16 +4262,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L76" s="5">
         <v>2</v>
@@ -4120,6 +4280,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J63" r:id="rId1" xr:uid="{F4001A4E-147C-4DA1-B793-B80C3CDB6A5D}"/>
+    <hyperlink ref="J64" r:id="rId2" xr:uid="{1C54E67C-A897-4CE8-8DDB-68404103A173}"/>
+    <hyperlink ref="J57" r:id="rId3" xr:uid="{AC12A72D-B1A4-4ADA-9031-1C383FCAA1B3}"/>
+    <hyperlink ref="J60" r:id="rId4" xr:uid="{C27C1531-6963-475C-918B-15E643DEBDF8}"/>
+    <hyperlink ref="J55" r:id="rId5" xr:uid="{D099FDCA-86C8-4BCB-9BE9-0EB0F078721B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12B7F36-292D-43C1-98A1-FE0B2D80214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF14FAD-A8C2-456D-AEEF-4F59873EC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="448">
   <si>
     <t>dimension_id</t>
   </si>
@@ -680,15 +680,9 @@
     <t>attribute-function</t>
   </si>
   <si>
-    <t>motion</t>
-  </si>
-  <si>
     <t>Attribute Function</t>
   </si>
   <si>
-    <t>Motion</t>
-  </si>
-  <si>
     <t>Attribute Dimensions</t>
   </si>
   <si>
@@ -1365,6 +1359,15 @@
   </si>
   <si>
     <t>"/Design-Space-Explorer/videos/patterns.mp4"</t>
+  </si>
+  <si>
+    <t>temporality</t>
+  </si>
+  <si>
+    <t>Temporality</t>
+  </si>
+  <si>
+    <t>Physical attributes can be static or dynamic, and many physically-inspired effects can be shown in either form. Even in dynamic visualizations, some elements may remain fixed, while in static images, processes such as breaking or unfolding can still be suggested through progressive states. Temporality expands the design space by allowing visualizations to represent both states and processes.</t>
   </si>
 </sst>
 </file>
@@ -1823,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1849,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>28</v>
@@ -1869,16 +1872,16 @@
     </row>
     <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -1887,7 +1890,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1895,16 +1898,16 @@
     </row>
     <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>24</v>
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
@@ -1953,10 +1956,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
@@ -1979,7 +1982,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -1991,7 +1994,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -2005,7 +2008,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D9" t="s">
         <v>52</v>
@@ -2031,7 +2034,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -2057,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -2083,7 +2086,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2133,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -2159,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -2185,19 +2188,19 @@
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D16" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>221</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2205,23 +2208,25 @@
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>218</v>
+        <v>445</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>447</v>
+      </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>446</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2235,16 +2240,16 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>216</v>
@@ -2304,10 +2309,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>26</v>
@@ -2327,12 +2332,12 @@
         <v>63</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
@@ -2360,7 +2365,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
@@ -2383,7 +2388,7 @@
         <v>68</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2409,12 +2414,12 @@
         <v>70</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
@@ -2437,7 +2442,7 @@
         <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2463,12 +2468,12 @@
         <v>74</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
@@ -2586,27 +2591,27 @@
     </row>
     <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -2614,27 +2619,27 @@
     </row>
     <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>353</v>
-      </c>
       <c r="C13" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L13" s="5">
         <v>2</v>
@@ -2642,20 +2647,20 @@
     </row>
     <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -2670,13 +2675,13 @@
     </row>
     <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -2690,7 +2695,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -2698,13 +2703,13 @@
     </row>
     <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>101</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D16" t="s">
         <v>102</v>
@@ -2718,7 +2723,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
@@ -2726,13 +2731,13 @@
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s">
         <v>104</v>
@@ -2744,7 +2749,7 @@
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L17" s="5">
         <v>3</v>
@@ -2761,7 +2766,7 @@
         <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
@@ -2772,7 +2777,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="6"/>
       <c r="K18" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
@@ -2800,7 +2805,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="6"/>
       <c r="K19" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
@@ -2856,7 +2861,7 @@
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
@@ -2932,7 +2937,7 @@
         <v>155</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>182</v>
@@ -3013,10 +3018,10 @@
         <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -3076,19 +3081,19 @@
         <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
@@ -3102,16 +3107,16 @@
         <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>198</v>
@@ -3123,16 +3128,16 @@
         <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3154,15 +3159,15 @@
         <v>60</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -3185,7 +3190,7 @@
         <v>59</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>194</v>
@@ -3222,10 +3227,10 @@
         <v>113</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C36" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D36" t="s">
         <v>164</v>
@@ -3234,10 +3239,10 @@
         <v>59</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L36" s="5"/>
     </row>
@@ -3246,10 +3251,10 @@
         <v>113</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C37" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
         <v>164</v>
@@ -3258,10 +3263,10 @@
         <v>59</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L37" s="5"/>
     </row>
@@ -3270,10 +3275,10 @@
         <v>113</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C38" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -3282,10 +3287,10 @@
         <v>59</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L38" s="5"/>
     </row>
@@ -3294,10 +3299,10 @@
         <v>113</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C39" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D39" t="s">
         <v>164</v>
@@ -3306,10 +3311,10 @@
         <v>59</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L39" s="5"/>
     </row>
@@ -3318,10 +3323,10 @@
         <v>113</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C40" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -3330,7 +3335,7 @@
         <v>59</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>191</v>
@@ -3342,10 +3347,10 @@
         <v>113</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C41" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D41" t="s">
         <v>164</v>
@@ -3354,10 +3359,10 @@
         <v>59</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L41" s="5"/>
     </row>
@@ -3366,10 +3371,10 @@
         <v>113</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D42" t="s">
         <v>164</v>
@@ -3378,7 +3383,7 @@
         <v>59</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>208</v>
@@ -3390,10 +3395,10 @@
         <v>113</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C43" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D43" t="s">
         <v>164</v>
@@ -3402,10 +3407,10 @@
         <v>59</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L43" s="5"/>
     </row>
@@ -3414,10 +3419,10 @@
         <v>113</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C44" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D44" t="s">
         <v>164</v>
@@ -3426,10 +3431,10 @@
         <v>59</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L44" s="5"/>
     </row>
@@ -3438,10 +3443,10 @@
         <v>113</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D45" t="s">
         <v>164</v>
@@ -3450,7 +3455,7 @@
         <v>59</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>200</v>
@@ -3462,10 +3467,10 @@
         <v>113</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D46" t="s">
         <v>164</v>
@@ -3474,10 +3479,10 @@
         <v>59</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L46" s="5"/>
     </row>
@@ -3486,10 +3491,10 @@
         <v>113</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D47" t="s">
         <v>164</v>
@@ -3498,10 +3503,10 @@
         <v>59</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L47" s="5"/>
     </row>
@@ -3551,7 +3556,7 @@
         <v>189</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L49" s="5">
         <v>2</v>
@@ -3623,10 +3628,10 @@
         <v>57</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L52" s="5">
         <v>2</v>
@@ -3672,16 +3677,16 @@
         <v>56</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H54" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="J54" t="s">
         <v>320</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="J54" t="s">
-        <v>322</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>196</v>
@@ -3707,13 +3712,13 @@
         <v>56</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K55" s="8" t="s">
         <v>197</v>
@@ -3727,23 +3732,23 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D56" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F56" s="6"/>
       <c r="H56" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I56" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="J56" t="s">
         <v>438</v>
-      </c>
-      <c r="J56" t="s">
-        <v>440</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>210</v>
@@ -3757,23 +3762,23 @@
         <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" t="s">
         <v>245</v>
-      </c>
-      <c r="C57" t="s">
-        <v>238</v>
-      </c>
-      <c r="D57" t="s">
-        <v>247</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K57" s="8" t="s">
         <v>212</v>
@@ -3787,29 +3792,29 @@
         <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C58" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J58" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L58" s="5">
         <v>5</v>
@@ -3820,26 +3825,26 @@
         <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D59" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J59" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L59" s="5">
         <v>6</v>
@@ -3850,26 +3855,26 @@
         <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L60" s="5">
         <v>7</v>
@@ -3892,16 +3897,16 @@
         <v>55</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H61" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="J61" t="s">
         <v>326</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="J61" t="s">
-        <v>328</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>208</v>
@@ -3927,16 +3932,16 @@
         <v>55</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J62" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K62" s="10" t="s">
         <v>209</v>
@@ -3950,29 +3955,29 @@
         <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H63" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="J63" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="I63" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>317</v>
-      </c>
       <c r="K63" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L63" s="5">
         <v>3</v>
@@ -3983,23 +3988,23 @@
         <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D64" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L64" s="5">
         <v>4</v>
@@ -4010,29 +4015,29 @@
         <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D65" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J65" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L65" s="5">
         <v>5</v>
@@ -4043,23 +4048,23 @@
         <v>43</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C66" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="I66" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="I66" s="10" t="s">
-        <v>422</v>
-      </c>
       <c r="J66" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K66" s="10" t="s">
         <v>202</v>
@@ -4073,23 +4078,23 @@
         <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="J67" t="s">
         <v>414</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J67" t="s">
-        <v>416</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>213</v>
@@ -4103,23 +4108,23 @@
         <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D68" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J68" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K68" s="10" t="s">
         <v>195</v>
@@ -4133,26 +4138,26 @@
         <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C69" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D69" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I69" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="J69" t="s">
         <v>423</v>
       </c>
-      <c r="J69" t="s">
-        <v>425</v>
-      </c>
       <c r="K69" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L69" s="5">
         <v>9</v>
@@ -4214,13 +4219,13 @@
         <v>217</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D73" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L73" s="5">
         <v>1</v>
@@ -4231,13 +4236,13 @@
         <v>217</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D74" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L74" s="5">
         <v>2</v>
@@ -4245,16 +4250,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>218</v>
+        <v>445</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L75" s="5">
         <v>1</v>
@@ -4262,16 +4267,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>218</v>
+        <v>445</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L76" s="5">
         <v>2</v>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF14FAD-A8C2-456D-AEEF-4F59873EC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4DFCBC-CE16-4B7D-95BD-4010996ADAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="864" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="460">
   <si>
     <t>dimension_id</t>
   </si>
@@ -224,9 +224,6 @@
     <t>Collection</t>
   </si>
   <si>
-    <t>A meaningful grouping of marks or collections that encodes data.</t>
-  </si>
-  <si>
     <t>annotation</t>
   </si>
   <si>
@@ -311,18 +308,12 @@
     <t>Intermediate Proximity (Iconic)</t>
   </si>
   <si>
-    <t>The visual element shares some similar qualities or resembles in an intuitive way the associated data/theme.</t>
-  </si>
-  <si>
     <t>high-proximity-literal</t>
   </si>
   <si>
     <t>High Proximity (Literal)</t>
   </si>
   <si>
-    <t>The visual element is closely (physically/causally) connected to the data/theme.</t>
-  </si>
-  <si>
     <t>low-proximity-slightly-familiar</t>
   </si>
   <si>
@@ -332,18 +323,9 @@
     <t>intermediate-proximity-moderately-familiar</t>
   </si>
   <si>
-    <t>The visual element is moderately familiar.</t>
-  </si>
-  <si>
     <t>high-proximity-very-familiar</t>
   </si>
   <si>
-    <t>The visual element is very familiar from everyday experience.</t>
-  </si>
-  <si>
-    <t>The object's location within the composition.</t>
-  </si>
-  <si>
     <t>orientation</t>
   </si>
   <si>
@@ -359,9 +341,6 @@
     <t>The angular rotation or facing direction of an object.</t>
   </si>
   <si>
-    <t>The size of an object, which can be in length, surface or volume.</t>
-  </si>
-  <si>
     <t>surface</t>
   </si>
   <si>
@@ -491,84 +470,9 @@
     <t>Surface</t>
   </si>
   <si>
-    <t>The geometry's overall shape. It can be a recognizable shape (e.g. a star or a hand) or an abstract one.</t>
-  </si>
-  <si>
-    <t>Data is mapped to localized deformations on the object's surface, such as bumps, folds or extrusions.</t>
-  </si>
-  <si>
-    <t>Clearly separated materials applied to different areas or objects, often indicating distinct categories.</t>
-  </si>
-  <si>
-    <t>From isolated material changes to complex changes that communicate physical processes.</t>
-  </si>
-  <si>
-    <t>Extension or elongation of an object's form.</t>
-  </si>
-  <si>
-    <t>Rotational deformation along an axis.</t>
-  </si>
-  <si>
-    <t>Fragmentation into separate pieces.</t>
-  </si>
-  <si>
-    <t>Focus is on the number of objects that make up the population.</t>
-  </si>
-  <si>
-    <t>Focus is on how closely or widely the objects are distributed.</t>
-  </si>
-  <si>
-    <t>The spatial arrangement or topological patterns applied to objects inside the population.</t>
-  </si>
-  <si>
-    <t>Light sources and illumination affecting the scene.</t>
-  </si>
-  <si>
-    <t>Point of view, angle, lens distortion.</t>
-  </si>
-  <si>
-    <t>Spatial and contextual elements surrounding a subject.</t>
-  </si>
-  <si>
-    <t>Sequential changes over time, showing stages or phases of development.</t>
-  </si>
-  <si>
-    <t>The rate of change or motion, representing velocity or pace.</t>
-  </si>
-  <si>
-    <t>Periodic or recurring patterns in time, creating temporal structure.</t>
-  </si>
-  <si>
-    <t>Structures that emerge, enlarge, branch, or differentiate over time.</t>
-  </si>
-  <si>
-    <t>Degradation caused by breakdown, death, or deterioration of living matter.</t>
-  </si>
-  <si>
-    <t>Motion of bodies treated as undeformable solids under forces, constraints, and collisions.</t>
-  </si>
-  <si>
-    <t>Shape changes and fracture of solids under stress, including elastic and plastic deformation.</t>
-  </si>
-  <si>
-    <t>There is a weak semantic congruence between the data variable and the representation.</t>
-  </si>
-  <si>
-    <t>There is an intermediate semantic congruence between the data variable and the representation.</t>
-  </si>
-  <si>
-    <t>There is a strong semantic connection between the data variable and the representation.</t>
-  </si>
-  <si>
     <t>category_order</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/position.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/orientation.png"</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/design_space_static/size.png"</t>
   </si>
   <si>
@@ -581,21 +485,12 @@
     <t>"/Design-Space-Explorer/design_space_static/twist.png"</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/lighting.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/environment.png"</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/design_space_static/material.png"</t>
   </si>
   <si>
     <t>"/Design-Space-Explorer/design_space_static/stretch.png"</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/camera2.png"</t>
-  </si>
-  <si>
     <t>ex-002</t>
   </si>
   <si>
@@ -761,36 +656,18 @@
     <t>Movement caused by internal, biological processes.</t>
   </si>
   <si>
-    <t>Periodic, life-like oscillations that convey internal cycles of living systems. Examples: “breathing”,  pulse/heartbeat dilations, tremor or “shaking”, bioluminescent pulsing.</t>
-  </si>
-  <si>
-    <t>Spread of living agents across an object or host. Examples: mold / mycelium, bacterial growth on a surface, moss / lichen.</t>
-  </si>
-  <si>
-    <t>Pattern formation or coordinated behavior arising from local interactions among many simple units, without centralized control. Examples: flocking / swarming, Turing patterns, phyllotaxis packing.</t>
-  </si>
-  <si>
     <t>Biological stage transitions that change appearance, structure, or function. Examples: germination, metamorphosis, flowering / fruiting / seeding.</t>
   </si>
   <si>
     <t>Fluids</t>
   </si>
   <si>
-    <t>Phenomena related to liquid and gaseous flows, including diffusion and mixing phenomena.</t>
-  </si>
-  <si>
     <t>Burning &amp; Smoke</t>
   </si>
   <si>
-    <t>Oxidation-driven emission and transformation of matter producing flames or smoke.</t>
-  </si>
-  <si>
     <t>State Change</t>
   </si>
   <si>
-    <t>Appearance and shape changes caused by heat transfer, temperature gradients, and transformations between phases.</t>
-  </si>
-  <si>
     <t>Force Fields &amp; Particles</t>
   </si>
   <si>
@@ -803,18 +680,6 @@
     <t>Weathering</t>
   </si>
   <si>
-    <t>Long-term alteration of surfaces and structures by environmental exposure and mechanical/chemical processes.</t>
-  </si>
-  <si>
-    <t>Effects arising from light–matter interaction and light transport.</t>
-  </si>
-  <si>
-    <t>Repeating disturbances over time, either traveling through space (waves) or cycling in place (oscillations).</t>
-  </si>
-  <si>
-    <t>Motion and structure shaped by force fields, which can be electromagnetic-based, wind or abstract ones. The gravitational field is not included in this category and is classified in “Statics &amp; Dynamics”.</t>
-  </si>
-  <si>
     <t>weathering</t>
   </si>
   <si>
@@ -875,66 +740,12 @@
     <t>Inflate / Deflate</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/inflate.png"</t>
-  </si>
-  <si>
     <t>The type of the visual element.</t>
   </si>
   <si>
     <t>The element’s structural level within the visualization’s composition, based on what it belongs to. Levels increase as you move from individual items to nested groups.</t>
   </si>
   <si>
-    <t>Degree to which the physically-inspired representation is semantically related to the associated data variables or theme. Indexical mappings are closest, symbolic are furthest, and iconic fall in between.</t>
-  </si>
-  <si>
-    <t>Degree to which the metaphor matches audiences’ real-world knowledge and experience. It corresponds to the level of familiarity with the mental image and perceptual affordances conveyed by the visual element.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The attribute function specifies the primary role a physical attribute plays in the visualization. </t>
-  </si>
-  <si>
-    <t>Positional or geometric traits of an object.</t>
-  </si>
-  <si>
-    <t>Attributes relating to the overall shape or surface details of a geometry.</t>
-  </si>
-  <si>
-    <t>Attributes referring to the substance an object appears to be made of.</t>
-  </si>
-  <si>
-    <t>Deformations or physical manipulations that affect an object’s form. Those deformations can be associated with the material state of an object. The change of form can arise from both implied external stimuli (e.g., a force deforming an object) or living mechanisms (e.g. the growth of a tree).</t>
-  </si>
-  <si>
-    <t>Patterns of repetition, accumulation, or dispersion of multiple objects.</t>
-  </si>
-  <si>
-    <t>The attribute appears to arise from living bodies or biological processes.</t>
-  </si>
-  <si>
-    <t>The attribute appears to be produced by physics or chemical phenomena.</t>
-  </si>
-  <si>
-    <t>Degree to which an encoding’s perceived meaning directly conveys the encoded data variable. It is low when the mapping is immediately interpretable and high when it is arbitrary or requires substantial inference.</t>
-  </si>
-  <si>
-    <t>A non-encoding element that explicitly attaches to a target (mark, collection, guide, or other chart component) to explain, emphasize, or direct attention to it. It can take the form of a shape, highlight, or image.</t>
-  </si>
-  <si>
-    <t>A non-encoding element that supports interpretation of the scale of the encodings. It can be an axis, a legend, or an anchor element that provides reference by comparison.</t>
-  </si>
-  <si>
-    <t>A non-encoding element that supports interpretation of the context of the dataset or the message of the visualization. It is neither an information nor a reference object and could be removed without affecting the interpretation of the representation and scale of the encodings. In contrast to an annotation, a decoration doesn’t attach to a target element.</t>
-  </si>
-  <si>
-    <t>A non-encoding element with the purpose of providing the “framing” for the other elements in the visualization. It often includes aspects of environment, background, point of view and lighting.</t>
-  </si>
-  <si>
-    <t>The visual element does not resemble the associated data/theme, the connection between them must be learned from conventions.</t>
-  </si>
-  <si>
-    <t>Cinematic, compositional and presentation elements.</t>
-  </si>
-  <si>
     <t>ex-030</t>
   </si>
   <si>
@@ -1034,9 +845,6 @@
     <t>"/Design-Space-Explorer/design_space_static/growth.png"</t>
   </si>
   <si>
-    <t>A mark is a graphical element that represents a data point. The visual properties of the mark map to data. A mark can also indirectly support data encodings when it functions as a unit within a collection and the data mapping occurs at the collection level.</t>
-  </si>
-  <si>
     <t>"/Design-Space-Explorer/design_space_static/mark.png"</t>
   </si>
   <si>
@@ -1055,12 +863,6 @@
     <t>"/Design-Space-Explorer/design_space_static/count.png"</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/speed.png"</t>
-  </si>
-  <si>
-    <t>This dimension focuses on photorealism in digital media: material appearance, lighting and shading, texture detail, shadows, and depth cues (e.g., perspective). It evaluates how “photo-like” the element looks, independent of what it represents or how abstract this representation may be. We also don’t evaluate how well its motion matches what it represents (captured in real-world representation).</t>
-  </si>
-  <si>
     <t>Visual Realism</t>
   </si>
   <si>
@@ -1085,24 +887,12 @@
     <t>high-realism</t>
   </si>
   <si>
-    <t>The element is highly stylized, with minimal or no attempt to imitate a photorealistic appearance.</t>
-  </si>
-  <si>
-    <t>The element includes some realistic aspects, such as depth, lighting, or texture, but these are mixed with stylized aspects.</t>
-  </si>
-  <si>
-    <t>Strong resemblance to physical reality through detailed materials, lighting, shadows, and depth cues. Photographs of physical artefacts also belong to this category.</t>
-  </si>
-  <si>
     <t>High (Visually Realistic)</t>
   </si>
   <si>
     <t>Intermediate (Mixed Realism)</t>
   </si>
   <si>
-    <t>Low (Stylized)</t>
-  </si>
-  <si>
     <t>ex-014</t>
   </si>
   <si>
@@ -1247,15 +1037,6 @@
     <t>ex-009</t>
   </si>
   <si>
-    <t>Low (Unfamiliar)</t>
-  </si>
-  <si>
-    <t>Intermediate (Slightly Familiar)</t>
-  </si>
-  <si>
-    <t>High (Familiar)</t>
-  </si>
-  <si>
     <t>ex-032</t>
   </si>
   <si>
@@ -1367,7 +1148,293 @@
     <t>Temporality</t>
   </si>
   <si>
-    <t>Physical attributes can be static or dynamic, and many physically-inspired effects can be shown in either form. Even in dynamic visualizations, some elements may remain fixed, while in static images, processes such as breaking or unfolding can still be suggested through progressive states. Temporality expands the design space by allowing visualizations to represent both states and processes.</t>
+    <t>A mark represents a data point or unit of data through its visual properties, or contributes to a higher-level encoding when grouped into a collection. Marks occupy the lowest hierarchy level (level 1).</t>
+  </si>
+  <si>
+    <t>A collection is a grouping of marks or nested collections that encodes data. Collections support higher-level encodings and can appear at hierarchy levels 2, 3, ... depending on how many levels of grouping are present.
+    Collections may arise through; repetition of a data element, division of a data element into parts, or more general grouping/aggregation techniques.</t>
+  </si>
+  <si>
+    <t>An annotation is a supportive visual element that explicitly attaches to a target element in order to explain, emphasize, or direct attention to it. Annotations do not encode data themselves, but they help viewers interpret the encodings. Annotations may take the form of shapes, highlights, pointers, or image-based additions. Textual annotations are out of scope in this scheme.</t>
+  </si>
+  <si>
+    <t>A guide is a supportive visual element that helps viewers interpret the scale, magnitude, or meaning of a data encoding. Guides do not encode data themselves, but provide reference by comparison. Examples include: axes, legends, unit references, or recognizable comparison objects such as buildings, silhouettes, or containers. Use Guide when the element helps the viewer read or estimate values, sizes, or categories.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A decoration is a supportive visual element that contributes to the interpretation of the broader context, theme, or message of the visualization without directly helping viewers read the data values or scale. Decorations do not attach to a specific target. A decoration may reinforce atmosphere, theme, or narrative, and may incorporate physically-inspired cues, but could be removed without changing the basic interpretation of the representation or its scale. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scene captures the global framing of the visualization. It includes properties such as environment, viewpoint, lighting, background, and atmosphere that shape how all other elements are perceived.
+    Unlike conventional visualizations with abstract backgrounds, physically-inspired visualizations often place elements within more familiar or coherent environments. </t>
+  </si>
+  <si>
+    <t>Visual realism captures the degree to which a visual element’s appearance and, when applicable, behavior evoke the perceptual impression of a real-world entity or phenomenon. 
+This impression may arise from rendering cues such as material detail, texture, shadows, depth, and coherent lighting, as well as from motion that appears physically plausible. In this framework, realism is assessed at the level of individual visual elements, since physically-inspired visualizations often combine elements with different degrees of realism within the same scene. For dynamic visualizations, evaluate not only static appearance but also the extent to which the element’s movement matches viewers’ expectations of physical behavior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-world familiarity captures how clearly a visual element depicts a recognizable real-world entity in a way that aligns with viewers’ everyday knowledge and experience.
+Whereas visual realism concerns how convincingly an element looks or behaves, real-world familiarity concerns how familiar the depicted entity itself is. This dimension reflects whether viewers can readily identify what is shown and anticipate its typical perceptual or action affordances—for example, how it might feel, behave, or be handled. </t>
+  </si>
+  <si>
+    <t>Metaphorical proximity to data captures how closely a visual element relates to the data variable or theme it represents. This dimension describes the semantic distance between what is depicted and what is communicated. It draws on semiotic distinctions between symbolic, iconic, and literal/indexical relations, and captures how directly a representation’s visual form relates to the underlying data or theme.
+This dimension is independent of how realistically an element is rendered and how familiar it is as an object. A visual element may therefore be highly familiar or highly realistic, yet still only loosely connected to the data.</t>
+  </si>
+  <si>
+    <t>The element is highly stylized, with little attempt to imitate real-world optics or physics. It may use simplified shapes, flat colors, or abstract rendering, and if animated, its motion does not strongly appear physically plausible.</t>
+  </si>
+  <si>
+    <t>The element combines realistic and stylized cues. It may include some depth, shading, texture, or plausible motion, but these are mixed with more simplified or abstract visual qualities.</t>
+  </si>
+  <si>
+    <t>The element strongly evokes physical reality through detailed rendering and/or physically plausible behavior. Typical cues include rich material appearance, coherent lighting, shadows, depth, and motion that appears believable in physical terms. Photographs of physical artifacts also belong to this category.</t>
+  </si>
+  <si>
+    <t>The element suggests a recognizable real-world entity or category, but remains simplified, stylized, or somewhat ambiguous. Viewers may identify it, but the expected affordances are only partially conveyed or may vary across viewers.</t>
+  </si>
+  <si>
+    <t>The element clearly depicts a familiar real-world entity that most viewers can identify quickly and consistently. It evokes a strong shared sense of its typical perceptual and action affordances.</t>
+  </si>
+  <si>
+    <t>High (Very Familiar)</t>
+  </si>
+  <si>
+    <t>Low (Slightly Familiar)</t>
+  </si>
+  <si>
+    <t>Low (Highly stylized)</t>
+  </si>
+  <si>
+    <t>The visual element does not resemble the data variable or theme, and the connection must be learned through convention or external explanation. Use this when the relation between depiction and data is arbitrary or abstract.</t>
+  </si>
+  <si>
+    <t>The visual element is closely connected to the data variable or theme through physical, causal, or direct similarity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The visual element shares some salient qualities with the associated data variable or theme in an intuitive way, even if it is not literally the same thing. </t>
+  </si>
+  <si>
+    <t>Intermediate (Familiar)</t>
+  </si>
+  <si>
+    <t>Spatial attributes capture position, orientation, and size. These channels are well established in visualization, but in physically-inspired visualization they can also evoke physical conditions and be realized through diverse physical processes.</t>
+  </si>
+  <si>
+    <t>Geometry attributes describe a visual element’s overall shape and surface form. They range from recognizable real-world forms to abstract ones, and may also include localized deformations such as bumps, folds, or extrusions.</t>
+  </si>
+  <si>
+    <t>Material attributes describe the substance an element appears to be made of. This category extends appearance-based channels such as color, texture, and opacity by treating them not only as abstract visual variables, but also as cues to material identity and material change. Material attributes can therefore range from simple material assignments to more complex transformations that suggest physical processes such as charring, contamination, heating, or decay.</t>
+  </si>
+  <si>
+    <t>Structural attributes describe deformations and physical manipulations that alter an element’s form. They are used when the visible effect suggests a force or process acting on an existing form, rather than the form being treated as the element’s inherent shape.</t>
+  </si>
+  <si>
+    <t>Group and population attributes describe how multiple elements are repeated, distributed, and organized in space. They apply mainly to collections rather than individual marks. These attributes are especially relevant in unit visualizations, where data is encoded through the accumulation and distribution of discrete objects. In physically-inspired visualization, group organization often carries a stronger sense of physical structure and can suggest movement, accumulation, or environmental conditions.</t>
+  </si>
+  <si>
+    <t>Framing attributes describe the compositional choices that shape how physical cues are perceived. They include lighting, camera, and environment, and operate at the level of presentation rather than object form. These attributes help establish the broader spatial and atmospheric context in which the data is read.</t>
+  </si>
+  <si>
+    <t>Time attributes capture temporal qualities and are especially relevant in dynamic visualizations. Timeis treated as a way of expressing physically-inspired effects and dynamic processes.</t>
+  </si>
+  <si>
+    <t>Physical attributes may be static or dynamic. Even in dynamic visualizations, some attributes may remain fixed while others change over time. Temporality can change how an attribute is interpreted—for example, position becomes translation and orientation becomes rotation—while some attributes directly depict processes such as breaking or burning. Such processes can also be suggested in static images through progressive states.</t>
+  </si>
+  <si>
+    <t>Semantic congruence describes how directly the physical meaning of a data-encoding attribute supports interpretation of the data variable it represents. It captures how naturally a physical cue aligns with the meaning of the data, rather than how efficiently exact values can be read. Congruence is strong when a physical cue suggests a readily understandable mapping—for example, using size to encode quantity or cracks to encode structural damage. It is weak when the mapping feels physically arbitrary or requires substantial inference—for example, using material color to encode an unrelated categorical variable.</t>
+  </si>
+  <si>
+    <t>Biological mechanisms are used when the attribute appears to arise from living bodies or biological processes.</t>
+  </si>
+  <si>
+    <t>Physics-based and chemical mechanisms are used when the attribute appears to be produced by physical or chemical phenomena.</t>
+  </si>
+  <si>
+    <t>The attribute function specifies the primary role a physical attribute plays in the visualization. Physical attributes either encode data or provide context. Data-encoding attributes map to data variables. Contextual attributes support interpretation, realism, or narration without encoding values. An encoding attribute may also serve a contextual role when its physically-inspired cues are meaningfully related to the data theme.</t>
+  </si>
+  <si>
+    <t>The object’s location within the composition or scene.</t>
+  </si>
+  <si>
+    <t>The size of an object, including length, surface extent, or volume.</t>
+  </si>
+  <si>
+    <t>The element’s overall shape. It may be a recognizable shape (e.g.\ a star or a hand) or an abstract one.</t>
+  </si>
+  <si>
+    <t>Localized surface variation or deformation, such as bumps, folds, indentations, or extrusions.</t>
+  </si>
+  <si>
+    <t>Clearly separated materials applied to different objects or regions, often to mark different categories or roles.</t>
+  </si>
+  <si>
+    <t>From isolated material changes, such as in color or reflectance, to more complex changes that communicate physical processes, such as burning, decay, melting, or oxidation.</t>
+  </si>
+  <si>
+    <t>The form is elongated or pulled along one or more directions.</t>
+  </si>
+  <si>
+    <t>The form is rotated along its own axis, creating torsion.</t>
+  </si>
+  <si>
+    <t>The form is bent into or out of layered, creased, or collapsed configurations.</t>
+  </si>
+  <si>
+    <t>The form is divided into parts through slicing, cutting, or segmentation.</t>
+  </si>
+  <si>
+    <t>The form expands or contracts as if filled with or losing internal pressure.</t>
+  </si>
+  <si>
+    <t>The form fractures into separate pieces or visibly cracks apart.</t>
+  </si>
+  <si>
+    <t>The group and population focus is on the number of repeated elements.</t>
+  </si>
+  <si>
+    <t>The group and population  focus is on how closely elements are packed or dispersed.</t>
+  </si>
+  <si>
+    <t>Elements are arranged along a common axis or direction, creating an ordered linear structure.</t>
+  </si>
+  <si>
+    <t>Elements are layered vertically or horizontally so that they build on top of or against one another.</t>
+  </si>
+  <si>
+    <t>Elements are placed next to one another in close proximity without necessarily overlapping or forming a larger pile.</t>
+  </si>
+  <si>
+    <t>Elements are arranged along a directional path that suggests movement or travel through space.</t>
+  </si>
+  <si>
+    <t>Elements accumulate into a heap or mound, suggesting gravity-driven gathering or loose aggregation.</t>
+  </si>
+  <si>
+    <t>Elements gather into concentrated groups around one or more focal areas.</t>
+  </si>
+  <si>
+    <t>Elements are positioned according to relational or network structure rather than metric distance alone.</t>
+  </si>
+  <si>
+    <t>Elements are visually connected or attached to one another, suggesting cohesion or combination into a larger structure.</t>
+  </si>
+  <si>
+    <t>Elements are dispersed across space in a loose or irregular distribution.</t>
+  </si>
+  <si>
+    <t>Elements fill a bounded area efficiently, typically with little unused space and minimal overlap.</t>
+  </si>
+  <si>
+    <t>Elements are positioned according to geographic location or a map-based spatial reference.</t>
+  </si>
+  <si>
+    <t>Elements extend outward through a tree-like or radiating structure with diverging paths or offshoots.</t>
+  </si>
+  <si>
+    <t>Lighting conditions, intensity, direction, mood, or atmospheric effects.</t>
+  </si>
+  <si>
+    <t>Viewpoint, angle, framing, or other camera-related choices that affect perceived scale and depth.</t>
+  </si>
+  <si>
+    <t>The broader spatial or contextual setting in which the elements are situated.</t>
+  </si>
+  <si>
+    <t>The sequencing or unfolding of change over time.</t>
+  </si>
+  <si>
+    <t>The rate of change or movement.</t>
+  </si>
+  <si>
+    <t>Periodic or repeated temporal patterns.</t>
+  </si>
+  <si>
+    <t>Degradation caused by breakdown, death, or deterioration of living matter.
+Examples: rotting, biodegradation, wrinkling, decomposition.</t>
+  </si>
+  <si>
+    <t>Periodic, life-like oscillations that convey internal cycles of living systems.
+Examples: “breathing”, pulse/heartbeat dilations, tremor or “shaking”, bioluminescent
+pulsing.</t>
+  </si>
+  <si>
+    <t>Spread of living agents across an object or host.
+Examples: mold / mycelium, bacterial growth on a surface, moss / lichen.</t>
+  </si>
+  <si>
+    <t>Pattern formation or coordinated behavior arising from local interactions among many simple
+units, without centralized control.
+Examples: flocking / swarming, Turing patterns, phyllotaxis packing.</t>
+  </si>
+  <si>
+    <t>Motion of bodies treated as undeformable solids under forces, constraints, and collisions. The
+shape of the object remains essentially unchanged; the focus is on translation and rotation.
+Examples: gravity-driven fall, bouncing balls, projectile motion, rigid collisions, stacking
+and toppling, sliding or rolling without visible squish.</t>
+  </si>
+  <si>
+    <t>Shape changes and fracture of solids under stress, including elastic and plastic deformation.
+The focus is on how the material bends, stretches, compresses, twists, cracks, tears, or breaks
+in response to loads or impacts.
+Examples: twisting or bending beams, stretching or squashing objects, compression, plastic
+deformation, tearing, cutting, cracking and fracture.</t>
+  </si>
+  <si>
+    <t>Phenomena related to liquid and gaseous flows, including diffusion and mixing phenomena.
+Examples: ripples, droplets, mixing of liquids, flow, turbulence, vortices, jets.</t>
+  </si>
+  <si>
+    <t>Oxidation-driven emission and transformation of matter producing flames or smoke.
+Examples: smoke, burning, fire, explosion, heat.</t>
+  </si>
+  <si>
+    <t>Motion and structure shaped by force fields, which can be electromagnetic-based, wind or
+abstract ones. The gravitational field is not included in this category and is classified in
+“Statics &amp; Dynamics”.
+Examples: magnetic attraction / repulsion, wind, dust / pollen diffusion, particle movement.</t>
+  </si>
+  <si>
+    <t>Repeating disturbances over time, either traveling through space (waves) or cycling in place
+(oscillations).
+Examples: ripples on water, vibrating strings, springs, pulses.</t>
+  </si>
+  <si>
+    <t>The physical cue has a weak semantic connection to the data variable. The mapping feels
+arbitrary, conventional, or requires substantial inference.</t>
+  </si>
+  <si>
+    <t>The physical cue has a partially meaningful relation to the data variable, but the mapping is
+not immediately or strongly interpretable.</t>
+  </si>
+  <si>
+    <t>The physical cue has a strong semantic connection to the data variable and suggests an
+intuitive physical rationale for the mapping.</t>
+  </si>
+  <si>
+    <t>Long-term alteration of surfaces and structures by environmental exposure and mechanical/chemical processes. Examples: erosion, oxidation, decomposition, frosting.</t>
+  </si>
+  <si>
+    <t>Appearance and shape changes caused by heat transfer, temperature gradients, and transformations between phases.
+Examples: melting, freezing, evaporation, steam, frosting.</t>
+  </si>
+  <si>
+    <t>Structures that emerge, enlarge, branch, or differentiate over time, often following developmental rules.
+Examples: blooming flowers, branching trees or corals, cell division.</t>
+  </si>
+  <si>
+    <t>Effects arising from light–matter interaction and light transport.
+Examples: shadows, volumetric lighting (fog), subsurface scattering and translucency, caustics, refraction and lensing.</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/inflate.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/density.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/position.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/rotation.jpg"</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1509,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1477,6 +1544,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1797,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1826,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1838,7 +1908,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1852,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>28</v>
@@ -1864,24 +1934,24 @@
         <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="288" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>344</v>
+      <c r="C4" s="6" t="s">
+        <v>380</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>345</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -1890,24 +1960,24 @@
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>287</v>
+      <c r="C5" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>346</v>
+        <v>280</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>24</v>
@@ -1922,15 +1992,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>286</v>
+      <c r="C6" s="6" t="s">
+        <v>382</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
@@ -1956,10 +2026,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>308</v>
+        <v>245</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
@@ -1982,7 +2052,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>290</v>
+        <v>396</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -1994,7 +2064,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -2008,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>291</v>
+        <v>397</v>
       </c>
       <c r="D9" t="s">
         <v>52</v>
@@ -2034,7 +2104,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>292</v>
+        <v>398</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -2054,13 +2124,13 @@
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B11" s="5">
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>293</v>
+        <v>399</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -2086,7 +2156,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>302</v>
+        <v>400</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2111,7 +2181,9 @@
       <c r="B13" s="5">
         <v>2</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>401</v>
+      </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
@@ -2136,7 +2208,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>294</v>
+        <v>404</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -2162,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>295</v>
+        <v>405</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -2182,25 +2254,25 @@
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>288</v>
+        <v>406</v>
       </c>
       <c r="D16" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2208,25 +2280,25 @@
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>373</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2240,19 +2312,19 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -2309,10 +2381,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>316</v>
+        <v>253</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>26</v>
@@ -2321,7 +2393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -2331,25 +2403,25 @@
       <c r="C2" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>336</v>
+      <c r="D2" s="6" t="s">
+        <v>374</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>337</v>
+        <v>273</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="8" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" s="5" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -2359,19 +2431,19 @@
       <c r="C3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>66</v>
+      <c r="D3" s="6" t="s">
+        <v>375</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>338</v>
+        <v>274</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="8" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2382,13 +2454,13 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>297</v>
+        <v>376</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2397,7 +2469,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
       <c r="K4" s="8" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2408,24 +2480,24 @@
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>298</v>
+        <v>377</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>339</v>
+        <v>275</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
       <c r="K5" s="8" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="L5" s="5">
         <v>4</v>
@@ -2436,13 +2508,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>299</v>
+        <v>378</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2451,35 +2523,35 @@
       <c r="I6" s="8"/>
       <c r="J6" s="6"/>
       <c r="K6" s="8" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="L6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>300</v>
+      <c r="D7" s="6" t="s">
+        <v>379</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>340</v>
+        <v>276</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
       <c r="K7" s="8" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="L7" s="5">
         <v>6</v>
@@ -2490,16 +2562,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -2516,16 +2588,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" t="s">
         <v>80</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -2542,16 +2614,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2568,16 +2640,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" t="s">
         <v>88</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2591,27 +2663,27 @@
     </row>
     <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="D12" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -2619,27 +2691,27 @@
     </row>
     <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>357</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8" t="s">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="L13" s="5">
         <v>2</v>
@@ -2647,27 +2719,27 @@
     </row>
     <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="D14" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
       <c r="J14" s="6"/>
       <c r="K14" s="8" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="L14" s="5">
         <v>3</v>
@@ -2675,16 +2747,16 @@
     </row>
     <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
@@ -2695,7 +2767,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -2703,16 +2775,16 @@
     </row>
     <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
@@ -2723,7 +2795,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
@@ -2731,16 +2803,16 @@
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>387</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
@@ -2749,7 +2821,7 @@
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="L17" s="5">
         <v>3</v>
@@ -2760,13 +2832,13 @@
         <v>29</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="D18" t="s">
-        <v>301</v>
+        <v>391</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
@@ -2777,7 +2849,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="6"/>
       <c r="K18" s="8" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
@@ -2788,13 +2860,13 @@
         <v>29</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>393</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
@@ -2805,7 +2877,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="6"/>
       <c r="K19" s="8" t="s">
-        <v>411</v>
+        <v>338</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
@@ -2816,13 +2888,13 @@
         <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>392</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
@@ -2833,7 +2905,7 @@
       <c r="I20" s="8"/>
       <c r="J20" s="6"/>
       <c r="K20" s="8" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="L20" s="5">
         <v>3</v>
@@ -2850,18 +2922,18 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>407</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>179</v>
+        <v>458</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>305</v>
+        <v>242</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
@@ -2872,24 +2944,24 @@
         <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>180</v>
+        <v>459</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="L22" s="5">
         <v>2</v>
@@ -2900,24 +2972,24 @@
         <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>408</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="I23" s="9"/>
       <c r="K23" s="8" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="L23" s="5">
         <v>3</v>
@@ -2934,16 +3006,16 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
+        <v>409</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="L24" s="5">
         <v>1</v>
@@ -2954,22 +3026,22 @@
         <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>410</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="L25" s="5">
         <v>2</v>
@@ -2980,22 +3052,22 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>411</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="L26" s="5">
         <v>1</v>
@@ -3006,22 +3078,22 @@
         <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>412</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -3032,22 +3104,22 @@
         <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>413</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="L28" s="5">
         <v>1</v>
@@ -3058,19 +3130,19 @@
         <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>414</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="L29" s="5">
         <v>2</v>
@@ -3081,24 +3153,27 @@
         <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>277</v>
+        <v>232</v>
+      </c>
+      <c r="D30" t="s">
+        <v>415</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
       <c r="K30" s="8" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="L30" s="5"/>
     </row>
@@ -3107,19 +3182,22 @@
         <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>280</v>
+        <v>235</v>
+      </c>
+      <c r="D31" t="s">
+        <v>416</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="L31" s="5"/>
     </row>
@@ -3128,16 +3206,19 @@
         <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>282</v>
+        <v>237</v>
+      </c>
+      <c r="D32" t="s">
+        <v>417</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>283</v>
+        <v>456</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3147,27 +3228,27 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>418</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -3175,48 +3256,51 @@
     </row>
     <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="L34" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>420</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>59</v>
       </c>
+      <c r="G35" s="6" t="s">
+        <v>457</v>
+      </c>
       <c r="K35" s="8" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="L35" s="5">
         <v>2</v>
@@ -3224,365 +3308,359 @@
     </row>
     <row r="36" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="C36" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>386</v>
+        <v>316</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="C37" t="s">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>398</v>
+        <v>328</v>
       </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="C38" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>421</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="C39" t="s">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>432</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="C40" t="s">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>426</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="C41" t="s">
-        <v>384</v>
+        <v>314</v>
       </c>
       <c r="D41" t="s">
-        <v>164</v>
+        <v>431</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>371</v>
+        <v>301</v>
       </c>
       <c r="C42" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>430</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="C43" t="s">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>425</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="C44" t="s">
-        <v>381</v>
+        <v>311</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>429</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="C45" t="s">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>395</v>
+        <v>325</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>375</v>
+        <v>305</v>
       </c>
       <c r="C46" t="s">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="D46" t="s">
-        <v>164</v>
+        <v>427</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>396</v>
+        <v>326</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="C47" t="s">
-        <v>383</v>
+        <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>424</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>433</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>185</v>
-      </c>
+      <c r="G48" s="6"/>
       <c r="K48" s="10" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="L48" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>166</v>
+        <v>434</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>189</v>
-      </c>
+      <c r="G49" s="6"/>
       <c r="K49" s="10" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="L49" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>435</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>186</v>
-      </c>
+      <c r="G50" s="6"/>
       <c r="K50" s="10" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="L50" s="5">
         <v>3</v>
@@ -3593,45 +3671,43 @@
         <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>436</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>57</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="L51" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>437</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>343</v>
-      </c>
+      <c r="G52" s="6"/>
       <c r="K52" s="10" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="L52" s="5">
         <v>2</v>
@@ -3642,86 +3718,86 @@
         <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>438</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>57</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="L53" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
-      </c>
-      <c r="D54" t="s">
-        <v>171</v>
+        <v>133</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>454</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>335</v>
+        <v>272</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
       <c r="J54" t="s">
-        <v>320</v>
+        <v>257</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="L54" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
-      </c>
-      <c r="D55" t="s">
-        <v>172</v>
+        <v>132</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>439</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>56</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>435</v>
+        <v>362</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>433</v>
+        <v>360</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>197</v>
+        <v>162</v>
       </c>
       <c r="L55" s="5">
         <v>2</v>
@@ -3732,56 +3808,56 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D56" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6"/>
       <c r="H56" s="6" t="s">
-        <v>437</v>
+        <v>364</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>436</v>
+        <v>363</v>
       </c>
       <c r="J56" t="s">
-        <v>438</v>
+        <v>365</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="L56" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>236</v>
-      </c>
-      <c r="D57" t="s">
-        <v>245</v>
+        <v>201</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>440</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
-        <v>428</v>
+        <v>355</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>427</v>
+        <v>354</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="L57" s="5">
         <v>4</v>
@@ -3792,59 +3868,59 @@
         <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
-      </c>
-      <c r="D58" t="s">
-        <v>246</v>
+        <v>202</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>441</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>334</v>
+        <v>271</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>443</v>
+        <v>370</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="J58" t="s">
-        <v>440</v>
+        <v>367</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="L58" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="C59" t="s">
-        <v>238</v>
-      </c>
-      <c r="D59" t="s">
-        <v>247</v>
+        <v>203</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>442</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
-        <v>444</v>
+        <v>371</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>441</v>
+        <v>368</v>
       </c>
       <c r="J59" t="s">
-        <v>442</v>
+        <v>369</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="L59" s="5">
         <v>6</v>
@@ -3855,156 +3931,156 @@
         <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C60" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="D60" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="L60" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" t="s">
-        <v>173</v>
+        <v>131</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>443</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>333</v>
+        <v>270</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>324</v>
+        <v>261</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>325</v>
+        <v>262</v>
       </c>
       <c r="J61" t="s">
-        <v>326</v>
+        <v>263</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="L61" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" t="s">
         <v>130</v>
       </c>
-      <c r="C62" t="s">
-        <v>137</v>
-      </c>
-      <c r="D62" t="s">
-        <v>174</v>
+      <c r="D62" s="14" t="s">
+        <v>444</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>332</v>
+        <v>269</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>323</v>
+        <v>260</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="J62" t="s">
-        <v>322</v>
+        <v>259</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="L62" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>269</v>
+        <v>224</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
-      </c>
-      <c r="D63" t="s">
-        <v>250</v>
+        <v>211</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>330</v>
+        <v>267</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="L63" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>268</v>
+        <v>223</v>
       </c>
       <c r="C64" t="s">
-        <v>251</v>
-      </c>
-      <c r="D64" t="s">
-        <v>252</v>
+        <v>212</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>446</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>417</v>
+        <v>344</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>415</v>
+        <v>342</v>
       </c>
       <c r="L64" s="5">
         <v>4</v>
@@ -4015,200 +4091,200 @@
         <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>267</v>
+        <v>222</v>
       </c>
       <c r="C65" t="s">
-        <v>253</v>
-      </c>
-      <c r="D65" t="s">
-        <v>254</v>
+        <v>213</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>453</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>331</v>
+        <v>268</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>329</v>
+        <v>266</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>327</v>
+        <v>264</v>
       </c>
       <c r="J65" t="s">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="L65" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="C66" t="s">
-        <v>255</v>
-      </c>
-      <c r="D66" t="s">
-        <v>262</v>
+        <v>214</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>447</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
-        <v>418</v>
+        <v>345</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>420</v>
+        <v>347</v>
       </c>
       <c r="J66" t="s">
-        <v>419</v>
+        <v>346</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="L66" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="C67" t="s">
-        <v>256</v>
-      </c>
-      <c r="D67" t="s">
-        <v>261</v>
+        <v>215</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>448</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
-        <v>412</v>
+        <v>339</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J67" t="s">
-        <v>414</v>
+        <v>341</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="L67" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="C68" t="s">
-        <v>257</v>
-      </c>
-      <c r="D68" t="s">
-        <v>260</v>
+        <v>216</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>455</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>426</v>
+        <v>353</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>425</v>
+        <v>352</v>
       </c>
       <c r="J68" t="s">
-        <v>424</v>
+        <v>351</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="L68" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
-      </c>
-      <c r="D69" t="s">
-        <v>259</v>
+        <v>217</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>452</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>421</v>
+        <v>348</v>
       </c>
       <c r="J69" t="s">
-        <v>423</v>
+        <v>350</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="L69" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>136</v>
-      </c>
-      <c r="D70" t="s">
-        <v>175</v>
+        <v>129</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>449</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
-      </c>
-      <c r="D71" t="s">
-        <v>176</v>
+        <v>128</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>450</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" t="s">
-        <v>177</v>
+        <v>127</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>451</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>
@@ -4216,16 +4292,16 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="L73" s="5">
         <v>1</v>
@@ -4233,16 +4309,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="D74" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="L74" s="5">
         <v>2</v>
@@ -4250,16 +4326,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="L75" s="5">
         <v>1</v>
@@ -4267,16 +4343,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="L76" s="5">
         <v>2</v>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4DFCBC-CE16-4B7D-95BD-4010996ADAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7AF360-3427-44C8-A14A-A03872ACF0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="864" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="17172" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -1258,9 +1258,6 @@
     <t>The size of an object, including length, surface extent, or volume.</t>
   </si>
   <si>
-    <t>The element’s overall shape. It may be a recognizable shape (e.g.\ a star or a hand) or an abstract one.</t>
-  </si>
-  <si>
     <t>Localized surface variation or deformation, such as bumps, folds, indentations, or extrusions.</t>
   </si>
   <si>
@@ -1435,6 +1432,9 @@
   </si>
   <si>
     <t>"/Design-Space-Explorer/design_space_static/rotation.jpg"</t>
+  </si>
+  <si>
+    <t>The element’s overall shape. It may be a recognizable shape (e.g., a star or a hand) or an abstract one.</t>
   </si>
 </sst>
 </file>
@@ -2929,7 +2929,7 @@
         <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
@@ -2957,7 +2957,7 @@
         <v>35</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
@@ -3006,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>244</v>
@@ -3032,7 +3032,7 @@
         <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>37</v>
@@ -3058,7 +3058,7 @@
         <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>61</v>
@@ -3084,7 +3084,7 @@
         <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>61</v>
@@ -3110,7 +3110,7 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>60</v>
@@ -3136,7 +3136,7 @@
         <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>60</v>
@@ -3159,7 +3159,7 @@
         <v>232</v>
       </c>
       <c r="D30" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>60</v>
@@ -3188,7 +3188,7 @@
         <v>235</v>
       </c>
       <c r="D31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>60</v>
@@ -3212,13 +3212,13 @@
         <v>237</v>
       </c>
       <c r="D32" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3234,7 +3234,7 @@
         <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>60</v>
@@ -3265,7 +3265,7 @@
         <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>59</v>
@@ -3291,13 +3291,13 @@
         <v>140</v>
       </c>
       <c r="D35" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>160</v>
@@ -3317,7 +3317,7 @@
         <v>295</v>
       </c>
       <c r="D36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>59</v>
@@ -3341,7 +3341,7 @@
         <v>297</v>
       </c>
       <c r="D37" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>59</v>
@@ -3365,7 +3365,7 @@
         <v>293</v>
       </c>
       <c r="D38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>59</v>
@@ -3389,7 +3389,7 @@
         <v>307</v>
       </c>
       <c r="D39" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>59</v>
@@ -3413,7 +3413,7 @@
         <v>308</v>
       </c>
       <c r="D40" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>59</v>
@@ -3437,7 +3437,7 @@
         <v>314</v>
       </c>
       <c r="D41" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>59</v>
@@ -3461,7 +3461,7 @@
         <v>309</v>
       </c>
       <c r="D42" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>59</v>
@@ -3485,7 +3485,7 @@
         <v>310</v>
       </c>
       <c r="D43" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>59</v>
@@ -3509,7 +3509,7 @@
         <v>311</v>
       </c>
       <c r="D44" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>59</v>
@@ -3533,7 +3533,7 @@
         <v>312</v>
       </c>
       <c r="D45" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>59</v>
@@ -3557,7 +3557,7 @@
         <v>315</v>
       </c>
       <c r="D46" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>59</v>
@@ -3581,7 +3581,7 @@
         <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>59</v>
@@ -3605,7 +3605,7 @@
         <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>58</v>
@@ -3629,7 +3629,7 @@
         <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>58</v>
@@ -3653,7 +3653,7 @@
         <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>58</v>
@@ -3677,7 +3677,7 @@
         <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>57</v>
@@ -3700,7 +3700,7 @@
         <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>57</v>
@@ -3724,7 +3724,7 @@
         <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>57</v>
@@ -3747,7 +3747,7 @@
         <v>133</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>56</v>
@@ -3782,7 +3782,7 @@
         <v>132</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>56</v>
@@ -3844,7 +3844,7 @@
         <v>201</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
@@ -3874,7 +3874,7 @@
         <v>202</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
@@ -3907,7 +3907,7 @@
         <v>203</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
@@ -3967,7 +3967,7 @@
         <v>131</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>55</v>
@@ -4002,7 +4002,7 @@
         <v>130</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>55</v>
@@ -4037,7 +4037,7 @@
         <v>211</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
@@ -4070,7 +4070,7 @@
         <v>212</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
@@ -4097,7 +4097,7 @@
         <v>213</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
@@ -4130,7 +4130,7 @@
         <v>214</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
@@ -4160,7 +4160,7 @@
         <v>215</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
@@ -4190,7 +4190,7 @@
         <v>216</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
@@ -4220,7 +4220,7 @@
         <v>217</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
@@ -4250,7 +4250,7 @@
         <v>129</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
@@ -4267,7 +4267,7 @@
         <v>128</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
@@ -4284,7 +4284,7 @@
         <v>127</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7AF360-3427-44C8-A14A-A03872ACF0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B1C086-1087-4066-8FD1-AA8C66F56BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3780" yWindow="17172" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="462">
   <si>
     <t>dimension_id</t>
   </si>
@@ -1195,15 +1195,6 @@
     <t>The element clearly depicts a familiar real-world entity that most viewers can identify quickly and consistently. It evokes a strong shared sense of its typical perceptual and action affordances.</t>
   </si>
   <si>
-    <t>High (Very Familiar)</t>
-  </si>
-  <si>
-    <t>Low (Slightly Familiar)</t>
-  </si>
-  <si>
-    <t>Low (Highly stylized)</t>
-  </si>
-  <si>
     <t>The visual element does not resemble the data variable or theme, and the connection must be learned through convention or external explanation. Use this when the relation between depiction and data is arbitrary or abstract.</t>
   </si>
   <si>
@@ -1211,9 +1202,6 @@
   </si>
   <si>
     <t xml:space="preserve">The visual element shares some salient qualities with the associated data variable or theme in an intuitive way, even if it is not literally the same thing. </t>
-  </si>
-  <si>
-    <t>Intermediate (Familiar)</t>
   </si>
   <si>
     <t>Spatial attributes capture position, orientation, and size. These channels are well established in visualization, but in physically-inspired visualization they can also evoke physical conditions and be realized through diverse physical processes.</t>
@@ -1435,6 +1423,24 @@
   </si>
   <si>
     <t>The element’s overall shape. It may be a recognizable shape (e.g., a star or a hand) or an abstract one.</t>
+  </si>
+  <si>
+    <t>Intermediate (Slightly Familiar)</t>
+  </si>
+  <si>
+    <t>High (Quite Familiar)</t>
+  </si>
+  <si>
+    <t>Low (Highly Stylized)</t>
+  </si>
+  <si>
+    <t>Low (Mostly Unfamiliar)</t>
+  </si>
+  <si>
+    <t>ex-071</t>
+  </si>
+  <si>
+    <t>ex-063</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>245</v>
@@ -2052,7 +2058,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2078,7 +2084,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D9" t="s">
         <v>52</v>
@@ -2104,7 +2110,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -2130,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -2156,7 +2162,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2182,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
@@ -2208,7 +2214,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -2234,7 +2240,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -2260,7 +2266,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D16" t="s">
         <v>183</v>
@@ -2286,7 +2292,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D17" t="s">
         <v>373</v>
@@ -2312,7 +2318,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
@@ -2669,7 +2675,7 @@
         <v>284</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
         <v>383</v>
@@ -2753,7 +2759,7 @@
         <v>96</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="D15" t="s">
         <v>97</v>
@@ -2781,7 +2787,7 @@
         <v>98</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>394</v>
+        <v>456</v>
       </c>
       <c r="D16" t="s">
         <v>386</v>
@@ -2795,7 +2801,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>330</v>
+        <v>460</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
@@ -2809,7 +2815,7 @@
         <v>99</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="D17" t="s">
         <v>387</v>
@@ -2838,7 +2844,7 @@
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
@@ -2866,7 +2872,7 @@
         <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
@@ -2894,7 +2900,7 @@
         <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
@@ -2922,14 +2928,14 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
@@ -2957,7 +2963,7 @@
         <v>35</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
@@ -2978,7 +2984,7 @@
         <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
@@ -3006,7 +3012,7 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>244</v>
@@ -3032,7 +3038,7 @@
         <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>37</v>
@@ -3058,7 +3064,7 @@
         <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>61</v>
@@ -3084,7 +3090,7 @@
         <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>61</v>
@@ -3110,7 +3116,7 @@
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>60</v>
@@ -3136,7 +3142,7 @@
         <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>60</v>
@@ -3159,7 +3165,7 @@
         <v>232</v>
       </c>
       <c r="D30" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>60</v>
@@ -3188,7 +3194,7 @@
         <v>235</v>
       </c>
       <c r="D31" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>60</v>
@@ -3212,13 +3218,13 @@
         <v>237</v>
       </c>
       <c r="D32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3234,7 +3240,7 @@
         <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>60</v>
@@ -3265,7 +3271,7 @@
         <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>59</v>
@@ -3291,13 +3297,13 @@
         <v>140</v>
       </c>
       <c r="D35" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>160</v>
@@ -3317,7 +3323,7 @@
         <v>295</v>
       </c>
       <c r="D36" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>59</v>
@@ -3341,7 +3347,7 @@
         <v>297</v>
       </c>
       <c r="D37" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>59</v>
@@ -3365,7 +3371,7 @@
         <v>293</v>
       </c>
       <c r="D38" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>59</v>
@@ -3389,7 +3395,7 @@
         <v>307</v>
       </c>
       <c r="D39" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>59</v>
@@ -3413,7 +3419,7 @@
         <v>308</v>
       </c>
       <c r="D40" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>59</v>
@@ -3437,7 +3443,7 @@
         <v>314</v>
       </c>
       <c r="D41" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>59</v>
@@ -3461,7 +3467,7 @@
         <v>309</v>
       </c>
       <c r="D42" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>59</v>
@@ -3485,7 +3491,7 @@
         <v>310</v>
       </c>
       <c r="D43" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>59</v>
@@ -3509,7 +3515,7 @@
         <v>311</v>
       </c>
       <c r="D44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>59</v>
@@ -3533,7 +3539,7 @@
         <v>312</v>
       </c>
       <c r="D45" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>59</v>
@@ -3557,7 +3563,7 @@
         <v>315</v>
       </c>
       <c r="D46" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>59</v>
@@ -3581,7 +3587,7 @@
         <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>59</v>
@@ -3605,7 +3611,7 @@
         <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>58</v>
@@ -3629,7 +3635,7 @@
         <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>58</v>
@@ -3653,7 +3659,7 @@
         <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>58</v>
@@ -3677,7 +3683,7 @@
         <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>57</v>
@@ -3700,7 +3706,7 @@
         <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>57</v>
@@ -3724,7 +3730,7 @@
         <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>57</v>
@@ -3747,7 +3753,7 @@
         <v>133</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>56</v>
@@ -3782,7 +3788,7 @@
         <v>132</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>56</v>
@@ -3844,7 +3850,7 @@
         <v>201</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
@@ -3874,7 +3880,7 @@
         <v>202</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
@@ -3907,7 +3913,7 @@
         <v>203</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
@@ -3967,7 +3973,7 @@
         <v>131</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>55</v>
@@ -4002,7 +4008,7 @@
         <v>130</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>55</v>
@@ -4037,7 +4043,7 @@
         <v>211</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
@@ -4070,7 +4076,7 @@
         <v>212</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
@@ -4097,7 +4103,7 @@
         <v>213</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
@@ -4130,7 +4136,7 @@
         <v>214</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
@@ -4143,7 +4149,7 @@
         <v>346</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>167</v>
+        <v>461</v>
       </c>
       <c r="L66" s="5">
         <v>6</v>
@@ -4160,7 +4166,7 @@
         <v>215</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
@@ -4190,7 +4196,7 @@
         <v>216</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
@@ -4220,7 +4226,7 @@
         <v>217</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
@@ -4250,7 +4256,7 @@
         <v>129</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
@@ -4267,7 +4273,7 @@
         <v>128</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
@@ -4284,7 +4290,7 @@
         <v>127</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B1C086-1087-4066-8FD1-AA8C66F56BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25C92A7-67AC-4AB0-A1C8-98A5AE5439FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="17172" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="17172" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>element-type</t>
   </si>
   <si>
-    <t>Element Type</t>
-  </si>
-  <si>
     <t>Visual Elements</t>
   </si>
   <si>
@@ -1441,6 +1438,9 @@
   </si>
   <si>
     <t>ex-063</t>
+  </si>
+  <si>
+    <t>Element Types</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1902,19 +1902,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1922,25 +1922,25 @@
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1948,25 +1948,25 @@
     </row>
     <row r="4" spans="1:8" ht="288" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1974,25 +1974,25 @@
     </row>
     <row r="5" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -2000,25 +2000,25 @@
     </row>
     <row r="6" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -2026,25 +2026,25 @@
     </row>
     <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="5">
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2052,13 +2052,13 @@
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="5">
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2067,10 +2067,10 @@
         <v>6</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -2078,25 +2078,25 @@
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5">
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H9">
         <v>3</v>
@@ -2104,25 +2104,25 @@
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5">
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -2130,25 +2130,25 @@
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="5">
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -2156,25 +2156,25 @@
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5">
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -2182,25 +2182,25 @@
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5">
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13">
         <v>7</v>
@@ -2208,25 +2208,25 @@
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5">
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="G14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2234,25 +2234,25 @@
     </row>
     <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5">
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -2260,25 +2260,25 @@
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D16" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>184</v>
-      </c>
       <c r="F16" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2286,25 +2286,25 @@
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2312,25 +2312,25 @@
     </row>
     <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5">
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -2387,13 +2387,13 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>5</v>
@@ -2404,24 +2404,24 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="D2" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
@@ -2432,24 +2432,24 @@
         <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2460,13 +2460,13 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2475,7 +2475,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
       <c r="K4" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2486,24 +2486,24 @@
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
       <c r="K5" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L5" s="5">
         <v>4</v>
@@ -2514,13 +2514,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2529,7 +2529,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="6"/>
       <c r="K6" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L6" s="5">
         <v>5</v>
@@ -2540,24 +2540,24 @@
         <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
       <c r="K7" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L7" s="5">
         <v>6</v>
@@ -2565,19 +2565,19 @@
     </row>
     <row r="8" spans="1:12" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -2591,19 +2591,19 @@
     </row>
     <row r="9" spans="1:12" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" t="s">
         <v>79</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -2617,19 +2617,19 @@
     </row>
     <row r="10" spans="1:12" s="5" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" t="s">
         <v>83</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -2643,19 +2643,19 @@
     </row>
     <row r="11" spans="1:12" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" t="s">
         <v>87</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2669,27 +2669,27 @@
     </row>
     <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -2697,27 +2697,27 @@
     </row>
     <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L13" s="5">
         <v>2</v>
@@ -2725,27 +2725,27 @@
     </row>
     <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="D14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
       <c r="J14" s="6"/>
       <c r="K14" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L14" s="5">
         <v>3</v>
@@ -2753,27 +2753,27 @@
     </row>
     <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D15" t="s">
         <v>96</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -2781,27 +2781,27 @@
     </row>
     <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
@@ -2809,25 +2809,25 @@
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L17" s="5">
         <v>3</v>
@@ -2835,27 +2835,27 @@
     </row>
     <row r="18" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="D18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="8"/>
       <c r="J18" s="6"/>
       <c r="K18" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
@@ -2863,27 +2863,27 @@
     </row>
     <row r="19" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="D19" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="8"/>
       <c r="J19" s="6"/>
       <c r="K19" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
@@ -2891,27 +2891,27 @@
     </row>
     <row r="20" spans="1:12" s="5" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>95</v>
-      </c>
       <c r="D20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="8"/>
       <c r="J20" s="6"/>
       <c r="K20" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L20" s="5">
         <v>3</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="21" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>14</v>
@@ -2928,18 +2928,18 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
@@ -2947,27 +2947,27 @@
     </row>
     <row r="22" spans="1:12" s="5" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L22" s="5">
         <v>2</v>
@@ -2975,27 +2975,27 @@
     </row>
     <row r="23" spans="1:12" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="D23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I23" s="9"/>
       <c r="K23" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L23" s="5">
         <v>3</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>16</v>
@@ -3012,16 +3012,16 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L24" s="5">
         <v>1</v>
@@ -3029,25 +3029,25 @@
     </row>
     <row r="25" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" t="s">
+        <v>404</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" t="s">
-        <v>405</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L25" s="5">
         <v>2</v>
@@ -3055,25 +3055,25 @@
     </row>
     <row r="26" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L26" s="5">
         <v>1</v>
@@ -3081,25 +3081,25 @@
     </row>
     <row r="27" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -3107,25 +3107,25 @@
     </row>
     <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L28" s="5">
         <v>1</v>
@@ -3133,22 +3133,22 @@
     </row>
     <row r="29" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L29" s="5">
         <v>2</v>
@@ -3156,105 +3156,105 @@
     </row>
     <row r="30" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D30" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
       <c r="K30" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L30" s="5"/>
     </row>
     <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>235</v>
-      </c>
       <c r="D31" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L31" s="5"/>
     </row>
     <row r="32" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="D32" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -3262,25 +3262,25 @@
     </row>
     <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L34" s="5">
         <v>1</v>
@@ -3288,25 +3288,25 @@
     </row>
     <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L35" s="5">
         <v>2</v>
@@ -3314,311 +3314,311 @@
     </row>
     <row r="36" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C36" t="s">
         <v>294</v>
       </c>
-      <c r="C36" t="s">
-        <v>295</v>
-      </c>
       <c r="D36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C37" t="s">
         <v>296</v>
       </c>
-      <c r="C37" t="s">
-        <v>297</v>
-      </c>
       <c r="D37" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C38" t="s">
         <v>292</v>
       </c>
-      <c r="C38" t="s">
-        <v>293</v>
-      </c>
       <c r="D38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D39" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D41" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D45" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D46" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D47" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G48" s="6"/>
       <c r="K48" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L48" s="5">
         <v>1</v>
@@ -3626,23 +3626,23 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G49" s="6"/>
       <c r="K49" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L49" s="5">
         <v>2</v>
@@ -3650,23 +3650,23 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="6"/>
       <c r="K50" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L50" s="5">
         <v>3</v>
@@ -3674,22 +3674,22 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L51" s="5">
         <v>1</v>
@@ -3697,23 +3697,23 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52" s="6"/>
       <c r="K52" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L52" s="5">
         <v>2</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L53" s="5">
         <v>3</v>
@@ -3744,34 +3744,34 @@
     </row>
     <row r="54" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H54" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I54" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="J54" t="s">
         <v>256</v>
       </c>
-      <c r="J54" t="s">
-        <v>257</v>
-      </c>
       <c r="K54" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L54" s="5">
         <v>1</v>
@@ -3779,31 +3779,31 @@
     </row>
     <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L55" s="5">
         <v>2</v>
@@ -3811,29 +3811,29 @@
     </row>
     <row r="56" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C56" t="s">
         <v>199</v>
       </c>
-      <c r="C56" t="s">
-        <v>200</v>
-      </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6"/>
       <c r="H56" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="J56" t="s">
         <v>364</v>
       </c>
-      <c r="I56" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="J56" t="s">
-        <v>365</v>
-      </c>
       <c r="K56" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L56" s="5">
         <v>3</v>
@@ -3841,29 +3841,29 @@
     </row>
     <row r="57" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="I57" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="I57" s="10" t="s">
-        <v>356</v>
-      </c>
       <c r="J57" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L57" s="5">
         <v>4</v>
@@ -3871,32 +3871,32 @@
     </row>
     <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I58" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="J58" t="s">
         <v>366</v>
       </c>
-      <c r="J58" t="s">
-        <v>367</v>
-      </c>
       <c r="K58" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L58" s="5">
         <v>5</v>
@@ -3904,29 +3904,29 @@
     </row>
     <row r="59" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I59" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="J59" t="s">
         <v>368</v>
       </c>
-      <c r="J59" t="s">
-        <v>369</v>
-      </c>
       <c r="K59" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L59" s="5">
         <v>6</v>
@@ -3934,29 +3934,29 @@
     </row>
     <row r="60" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L60" s="5">
         <v>7</v>
@@ -3964,34 +3964,34 @@
     </row>
     <row r="61" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H61" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I61" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I61" s="10" t="s">
+      <c r="J61" t="s">
         <v>262</v>
       </c>
-      <c r="J61" t="s">
-        <v>263</v>
-      </c>
       <c r="K61" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L61" s="5">
         <v>1</v>
@@ -3999,34 +3999,34 @@
     </row>
     <row r="62" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I62" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="J62" t="s">
         <v>258</v>
       </c>
-      <c r="J62" t="s">
-        <v>259</v>
-      </c>
       <c r="K62" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L62" s="5">
         <v>2</v>
@@ -4034,32 +4034,32 @@
     </row>
     <row r="63" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H63" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I63" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="J63" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="J63" s="12" t="s">
-        <v>252</v>
-      </c>
       <c r="K63" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L63" s="5">
         <v>3</v>
@@ -4067,26 +4067,26 @@
     </row>
     <row r="64" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C64" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L64" s="5">
         <v>4</v>
@@ -4094,32 +4094,32 @@
     </row>
     <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I65" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="J65" t="s">
         <v>264</v>
       </c>
-      <c r="J65" t="s">
-        <v>265</v>
-      </c>
       <c r="K65" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L65" s="5">
         <v>5</v>
@@ -4127,29 +4127,29 @@
     </row>
     <row r="66" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="J66" t="s">
         <v>345</v>
       </c>
-      <c r="I66" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J66" t="s">
-        <v>346</v>
-      </c>
       <c r="K66" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L66" s="5">
         <v>6</v>
@@ -4157,29 +4157,29 @@
     </row>
     <row r="67" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="I67" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="I67" s="10" t="s">
+      <c r="J67" t="s">
         <v>340</v>
       </c>
-      <c r="J67" t="s">
-        <v>341</v>
-      </c>
       <c r="K67" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L67" s="5">
         <v>7</v>
@@ -4187,29 +4187,29 @@
     </row>
     <row r="68" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J68" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L68" s="5">
         <v>8</v>
@@ -4217,29 +4217,29 @@
     </row>
     <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C69" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="J69" t="s">
         <v>349</v>
       </c>
-      <c r="I69" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="J69" t="s">
-        <v>350</v>
-      </c>
       <c r="K69" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L69" s="5">
         <v>9</v>
@@ -4247,16 +4247,16 @@
     </row>
     <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
@@ -4264,16 +4264,16 @@
     </row>
     <row r="71" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
@@ -4281,16 +4281,16 @@
     </row>
     <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C72" t="s">
         <v>126</v>
       </c>
-      <c r="C72" t="s">
-        <v>127</v>
-      </c>
       <c r="D72" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>
@@ -4298,16 +4298,16 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L73" s="5">
         <v>1</v>
@@ -4315,16 +4315,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L74" s="5">
         <v>2</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L75" s="5">
         <v>1</v>
@@ -4349,16 +4349,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L76" s="5">
         <v>2</v>

--- a/src/data/design_space.xlsx
+++ b/src/data/design_space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spili\Documents\GitHub\explorer\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25C92A7-67AC-4AB0-A1C8-98A5AE5439FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5FD6E6-128A-4D65-8B33-4BF0E2DE499F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="17172" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dimensions" sheetId="1" r:id="rId1"/>
@@ -470,24 +470,6 @@
     <t>category_order</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/size.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/shape.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/surface.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/twist.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/material.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/stretch.png"</t>
-  </si>
-  <si>
     <t>ex-002</t>
   </si>
   <si>
@@ -854,12 +836,6 @@
     <t>"/Design-Space-Explorer/design_space_static/scene.png"</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/design_space_static/cut.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/count.png"</t>
-  </si>
-  <si>
     <t>Visual Realism</t>
   </si>
   <si>
@@ -971,42 +947,6 @@
     <t>Topological Placement</t>
   </si>
   <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/adjacent_placement.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/bonding.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/alignment.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/branching.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/clustering.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/geographical_placement.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/packing.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/piling.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/scattering.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/stacking.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/topological_placement.png"</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/spatial_arrangement/trajectory.png"</t>
-  </si>
-  <si>
     <t>ex-064</t>
   </si>
   <si>
@@ -1026,9 +966,6 @@
   </si>
   <si>
     <t>ex-058</t>
-  </si>
-  <si>
-    <t>"/Design-Space-Explorer/design_space_static/material_transformation.png"</t>
   </si>
   <si>
     <t>ex-009</t>
@@ -1441,6 +1378,69 @@
   </si>
   <si>
     <t>Element Types</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/size.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/shape.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/surface.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/material.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/material_transformation.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/stretch.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/twist.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/cut.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/design_space_static/count.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/adjacent_placement.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/bonding.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/alignment.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/branching.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/clustering.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/geographical_placement.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/packing.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/piling.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/scattering.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/stacking.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/topological_placement.jpg"</t>
+  </si>
+  <si>
+    <t>"/Design-Space-Explorer/spatial_arrangement/trajectory.jpg"</t>
   </si>
 </sst>
 </file>
@@ -1902,10 +1902,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D2" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -1914,7 +1914,7 @@
         <v>24</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1928,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>27</v>
@@ -1940,7 +1940,7 @@
         <v>24</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1948,16 +1948,16 @@
     </row>
     <row r="4" spans="1:8" ht="288" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -1966,7 +1966,7 @@
         <v>24</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="5" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>23</v>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
@@ -2032,10 +2032,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
@@ -2058,7 +2058,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2070,7 +2070,7 @@
         <v>33</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -2084,7 +2084,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -2110,7 +2110,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -2136,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="D11" t="s">
         <v>49</v>
@@ -2162,7 +2162,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
@@ -2188,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
         <v>47</v>
@@ -2214,7 +2214,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
@@ -2240,7 +2240,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
@@ -2260,25 +2260,25 @@
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2286,25 +2286,25 @@
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="D17" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2318,19 +2318,19 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -2387,10 +2387,10 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>25</v>
@@ -2410,18 +2410,18 @@
         <v>62</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
       <c r="K2" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L2" s="5">
         <v>1</v>
@@ -2438,18 +2438,18 @@
         <v>64</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="8"/>
       <c r="J3" s="6"/>
       <c r="K3" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2466,7 +2466,7 @@
         <v>66</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2475,7 +2475,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="6"/>
       <c r="K4" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2492,18 +2492,18 @@
         <v>68</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="8"/>
       <c r="J5" s="6"/>
       <c r="K5" s="8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="L5" s="5">
         <v>4</v>
@@ -2520,7 +2520,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2529,7 +2529,7 @@
       <c r="I6" s="8"/>
       <c r="J6" s="6"/>
       <c r="K6" s="8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L6" s="5">
         <v>5</v>
@@ -2546,18 +2546,18 @@
         <v>72</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="8"/>
       <c r="J7" s="6"/>
       <c r="K7" s="8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="L7" s="5">
         <v>6</v>
@@ -2669,27 +2669,27 @@
     </row>
     <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="D12" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="8"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="L12" s="5">
         <v>1</v>
@@ -2697,27 +2697,27 @@
     </row>
     <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D13" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="L13" s="5">
         <v>2</v>
@@ -2725,27 +2725,27 @@
     </row>
     <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D14" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
       <c r="J14" s="6"/>
       <c r="K14" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="L14" s="5">
         <v>3</v>
@@ -2753,13 +2753,13 @@
     </row>
     <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -2773,7 +2773,7 @@
       <c r="I15" s="8"/>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -2781,16 +2781,16 @@
     </row>
     <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="D16" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
@@ -2801,7 +2801,7 @@
       <c r="I16" s="8"/>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="L16" s="5">
         <v>2</v>
@@ -2809,16 +2809,16 @@
     </row>
     <row r="17" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
@@ -2827,7 +2827,7 @@
       <c r="G17" s="6"/>
       <c r="I17" s="9"/>
       <c r="K17" s="8" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="L17" s="5">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
@@ -2855,7 +2855,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="6"/>
       <c r="K18" s="8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="L18" s="5">
         <v>1</v>
@@ -2872,7 +2872,7 @@
         <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
@@ -2883,7 +2883,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="6"/>
       <c r="K19" s="8" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="L19" s="5">
         <v>2</v>
@@ -2900,7 +2900,7 @@
         <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
@@ -2911,7 +2911,7 @@
       <c r="I20" s="8"/>
       <c r="J20" s="6"/>
       <c r="K20" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L20" s="5">
         <v>3</v>
@@ -2928,18 +2928,18 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="I21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L21" s="5">
         <v>1</v>
@@ -2963,11 +2963,11 @@
         <v>34</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="I22" s="9"/>
       <c r="K22" s="9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="L22" s="5">
         <v>2</v>
@@ -2984,18 +2984,18 @@
         <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>148</v>
+        <v>441</v>
       </c>
       <c r="I23" s="9"/>
       <c r="K23" s="8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="L23" s="5">
         <v>3</v>
@@ -3012,16 +3012,16 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>149</v>
+        <v>442</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="L24" s="5">
         <v>1</v>
@@ -3038,16 +3038,16 @@
         <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>150</v>
+        <v>443</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L25" s="5">
         <v>2</v>
@@ -3064,16 +3064,16 @@
         <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>152</v>
+        <v>444</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L26" s="5">
         <v>1</v>
@@ -3090,16 +3090,16 @@
         <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>334</v>
+        <v>445</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="L27" s="5">
         <v>2</v>
@@ -3116,22 +3116,22 @@
         <v>143</v>
       </c>
       <c r="D28" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>153</v>
+        <v>446</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="L28" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
@@ -3142,13 +3142,13 @@
         <v>142</v>
       </c>
       <c r="D29" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>151</v>
+        <v>447</v>
       </c>
       <c r="L29" s="5">
         <v>2</v>
@@ -3159,27 +3159,27 @@
         <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D30" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="6"/>
       <c r="K30" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="L30" s="5"/>
     </row>
@@ -3188,22 +3188,22 @@
         <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D31" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>276</v>
+        <v>448</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L31" s="5"/>
     </row>
@@ -3212,19 +3212,19 @@
         <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D32" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="5"/>
@@ -3240,21 +3240,21 @@
         <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="6"/>
       <c r="K33" s="8" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="L33" s="5">
         <v>3</v>
@@ -3271,16 +3271,16 @@
         <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>277</v>
+        <v>449</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="L34" s="5">
         <v>1</v>
@@ -3297,16 +3297,16 @@
         <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L35" s="5">
         <v>2</v>
@@ -3317,22 +3317,22 @@
         <v>105</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C36" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D36" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>315</v>
+        <v>450</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="L36" s="5"/>
     </row>
@@ -3341,22 +3341,22 @@
         <v>105</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C37" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D37" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>316</v>
+        <v>451</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="L37" s="5"/>
     </row>
@@ -3365,22 +3365,22 @@
         <v>105</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C38" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>317</v>
+        <v>452</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="L38" s="5"/>
     </row>
@@ -3389,22 +3389,22 @@
         <v>105</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D39" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>318</v>
+        <v>453</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L39" s="5"/>
     </row>
@@ -3413,22 +3413,22 @@
         <v>105</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C40" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D40" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>319</v>
+        <v>454</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="L40" s="5"/>
     </row>
@@ -3437,22 +3437,22 @@
         <v>105</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C41" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D41" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>320</v>
+        <v>455</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="L41" s="5"/>
     </row>
@@ -3461,22 +3461,22 @@
         <v>105</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" t="s">
         <v>300</v>
       </c>
-      <c r="C42" t="s">
-        <v>308</v>
-      </c>
       <c r="D42" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>321</v>
+        <v>456</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L42" s="5"/>
     </row>
@@ -3485,22 +3485,22 @@
         <v>105</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C43" t="s">
         <v>301</v>
       </c>
-      <c r="C43" t="s">
-        <v>309</v>
-      </c>
       <c r="D43" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>322</v>
+        <v>457</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="L43" s="5"/>
     </row>
@@ -3509,22 +3509,22 @@
         <v>105</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" t="s">
         <v>302</v>
       </c>
-      <c r="C44" t="s">
-        <v>310</v>
-      </c>
       <c r="D44" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>323</v>
+        <v>458</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="L44" s="5"/>
     </row>
@@ -3533,22 +3533,22 @@
         <v>105</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C45" t="s">
         <v>303</v>
       </c>
-      <c r="C45" t="s">
-        <v>311</v>
-      </c>
       <c r="D45" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>324</v>
+        <v>459</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="L45" s="5"/>
     </row>
@@ -3557,22 +3557,22 @@
         <v>105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C46" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D46" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>325</v>
+        <v>460</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L46" s="5"/>
     </row>
@@ -3581,22 +3581,22 @@
         <v>105</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C47" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>58</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>326</v>
+        <v>461</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="L47" s="5"/>
     </row>
@@ -3611,14 +3611,14 @@
         <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G48" s="6"/>
       <c r="K48" s="10" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="L48" s="5">
         <v>1</v>
@@ -3635,14 +3635,14 @@
         <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G49" s="6"/>
       <c r="K49" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="L49" s="5">
         <v>2</v>
@@ -3659,14 +3659,14 @@
         <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G50" s="6"/>
       <c r="K50" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="L50" s="5">
         <v>3</v>
@@ -3683,13 +3683,13 @@
         <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L51" s="5">
         <v>1</v>
@@ -3706,14 +3706,14 @@
         <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G52" s="6"/>
       <c r="K52" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L52" s="5">
         <v>2</v>
@@ -3730,13 +3730,13 @@
         <v>133</v>
       </c>
       <c r="D53" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L53" s="5">
         <v>3</v>
@@ -3753,25 +3753,25 @@
         <v>132</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="J54" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="L54" s="5">
         <v>1</v>
@@ -3788,22 +3788,22 @@
         <v>131</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>55</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="L55" s="5">
         <v>2</v>
@@ -3814,26 +3814,26 @@
         <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D56" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6"/>
       <c r="H56" s="6" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="J56" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="L56" s="5">
         <v>3</v>
@@ -3844,26 +3844,26 @@
         <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C57" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="F57" s="6"/>
       <c r="H57" s="6" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L57" s="5">
         <v>4</v>
@@ -3874,29 +3874,29 @@
         <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C58" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="J58" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="L58" s="5">
         <v>5</v>
@@ -3907,26 +3907,26 @@
         <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C59" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="F59" s="6"/>
       <c r="H59" s="6" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="J59" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L59" s="5">
         <v>6</v>
@@ -3937,26 +3937,26 @@
         <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" t="s">
         <v>203</v>
-      </c>
-      <c r="D60" t="s">
-        <v>209</v>
       </c>
       <c r="F60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="L60" s="5">
         <v>7</v>
@@ -3973,25 +3973,25 @@
         <v>130</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J61" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L61" s="5">
         <v>1</v>
@@ -4008,25 +4008,25 @@
         <v>129</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J62" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L62" s="5">
         <v>2</v>
@@ -4037,29 +4037,29 @@
         <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C63" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="L63" s="5">
         <v>3</v>
@@ -4070,23 +4070,23 @@
         <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C64" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="F64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="L64" s="5">
         <v>4</v>
@@ -4097,29 +4097,29 @@
         <v>42</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J65" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L65" s="5">
         <v>5</v>
@@ -4130,26 +4130,26 @@
         <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="F66" s="6"/>
       <c r="H66" s="6" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="J66" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="L66" s="5">
         <v>6</v>
@@ -4160,26 +4160,26 @@
         <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="F67" s="6"/>
       <c r="H67" s="6" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="J67" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="L67" s="5">
         <v>7</v>
@@ -4190,26 +4190,26 @@
         <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C68" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="F68" s="6"/>
       <c r="H68" s="6" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="J68" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="L68" s="5">
         <v>8</v>
@@ -4220,26 +4220,26 @@
         <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="F69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="J69" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L69" s="5">
         <v>9</v>
@@ -4256,7 +4256,7 @@
         <v>128</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="L70" s="5">
         <v>1</v>
@@ -4273,7 +4273,7 @@
         <v>127</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="L71" s="5">
         <v>2</v>
@@ -4290,7 +4290,7 @@
         <v>126</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="L72" s="5">
         <v>3</v>
@@ -4298,16 +4298,16 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D73" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L73" s="5">
         <v>1</v>
@@ -4315,16 +4315,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D74" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L74" s="5">
         <v>2</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="L75" s="5">
         <v>1</v>
@@ -4349,16 +4349,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="L76" s="5">
         <v>2</v>
